--- a/4_tables/4_reg_uwlsmra/meta_housing_uwlsmra_overall.xlsx
+++ b/4_tables/4_reg_uwlsmra/meta_housing_uwlsmra_overall.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.106** (0.035)</t>
+          <t>0.100** (0.035)</t>
         </is>
       </c>
     </row>
@@ -425,7 +425,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.097 (0.061)</t>
+          <t>-0.100 (0.059)</t>
         </is>
       </c>
     </row>
@@ -437,7 +437,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.001 (0.003)</t>
+          <t>0.002 (0.003)</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.146** (0.045)</t>
+          <t>0.137** (0.046)</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.053 (0.044)</t>
+          <t>0.044 (0.044)</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.092** (0.032)</t>
+          <t>-0.098** (0.033)</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.063 (0.043)</t>
+          <t>-0.092* (0.045)</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.283*** (0.042)</t>
+          <t>-0.267*** (0.044)</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.017 (0.032)</t>
+          <t>-0.021 (0.031)</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.005 (0.027)</t>
+          <t>-0.004 (0.027)</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.078** (0.027)</t>
+          <t>0.059* (0.027)</t>
         </is>
       </c>
     </row>
@@ -545,19 +545,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.096* (0.043)</t>
+          <t>0.105** (0.039)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-2.487* (0.952)</t>
+          <t>-0.976*** (0.264)</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>0.536</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -651,22 +651,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -676,8 +711,10 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
-        <v>0.000330545288265945</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -686,13 +723,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.06855782627163219</v>
+      </c>
+      <c r="F2">
+        <v>0.06844658518189936</v>
+      </c>
+      <c r="G2">
+        <v>-1.001625224829511</v>
+      </c>
+      <c r="H2">
+        <v>0.3165246333343902</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>0.0003305452882659248</v>
       </c>
     </row>
   </sheetData>
@@ -1110,19 +1165,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.0006448935077461382</v>
+        <v>0.0016702420768347</v>
       </c>
       <c r="C2">
-        <v>0.00336194943100665</v>
+        <v>0.003347409483759456</v>
       </c>
       <c r="D2">
-        <v>0.1918212992136057</v>
+        <v>0.4989655687295421</v>
       </c>
       <c r="E2">
-        <v>0.8482264593187592</v>
+        <v>0.618773618650907</v>
       </c>
       <c r="H2">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1131,17 +1186,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1152,19 +1207,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.06323695022619492</v>
+        <v>-0.05270789045125743</v>
       </c>
       <c r="C3">
-        <v>0.02372245653761812</v>
+        <v>0.02430783522782082</v>
       </c>
       <c r="D3">
-        <v>-2.665699908688474</v>
+        <v>-2.168349832770471</v>
       </c>
       <c r="E3">
-        <v>0.008808717032931927</v>
+        <v>0.03222873868814</v>
       </c>
       <c r="H3">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1173,17 +1228,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1194,19 +1249,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.1223612700731404</v>
+        <v>0.1081189812390079</v>
       </c>
       <c r="C4">
-        <v>0.03225815359745853</v>
+        <v>0.03296506218570294</v>
       </c>
       <c r="D4">
-        <v>3.793188897295741</v>
+        <v>3.27980516553976</v>
       </c>
       <c r="E4">
-        <v>0.0002405967086930631</v>
+        <v>0.001381429892368618</v>
       </c>
       <c r="H4">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1215,17 +1270,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1236,19 +1291,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.07569179319870559</v>
+        <v>0.06478817092307226</v>
       </c>
       <c r="C5">
-        <v>0.02774951667057808</v>
+        <v>0.02879872859105624</v>
       </c>
       <c r="D5">
-        <v>2.727679696092118</v>
+        <v>2.249688583238114</v>
       </c>
       <c r="E5">
-        <v>0.007397186221955758</v>
+        <v>0.02640569714721543</v>
       </c>
       <c r="H5">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1257,17 +1312,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1278,19 +1333,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.00835545245763019</v>
+        <v>0.002371540384609499</v>
       </c>
       <c r="C6">
-        <v>0.02485420114614292</v>
+        <v>0.02387192791861331</v>
       </c>
       <c r="D6">
-        <v>0.3361786769367503</v>
+        <v>0.09934431742148368</v>
       </c>
       <c r="E6">
-        <v>0.737359581653479</v>
+        <v>0.9210409185091104</v>
       </c>
       <c r="H6">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1299,17 +1354,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1320,19 +1375,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.001143799495046267</v>
+        <v>0.003287733706033608</v>
       </c>
       <c r="C7">
-        <v>0.02864653304256693</v>
+        <v>0.02786050833945639</v>
       </c>
       <c r="D7">
-        <v>-0.03992802526388284</v>
+        <v>0.1180069532822371</v>
       </c>
       <c r="E7">
-        <v>0.9682209673286022</v>
+        <v>0.9062716565845353</v>
       </c>
       <c r="H7">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1341,17 +1396,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1362,19 +1417,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.01292163509935453</v>
+        <v>0.009295975799638975</v>
       </c>
       <c r="C8">
-        <v>0.02081910084096766</v>
+        <v>0.02037943869274084</v>
       </c>
       <c r="D8">
-        <v>0.6206624963325719</v>
+        <v>0.4561448398944472</v>
       </c>
       <c r="E8">
-        <v>0.5360715449565854</v>
+        <v>0.6491612899325145</v>
       </c>
       <c r="H8">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1383,17 +1438,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1404,19 +1459,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.08633242940041365</v>
+        <v>0.08064428372708823</v>
       </c>
       <c r="C9">
-        <v>0.03582557226010367</v>
+        <v>0.03937224307085564</v>
       </c>
       <c r="D9">
-        <v>2.409799033316651</v>
+        <v>2.048252206051812</v>
       </c>
       <c r="E9">
-        <v>0.01757582630363968</v>
+        <v>0.0428527516081677</v>
       </c>
       <c r="H9">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1425,17 +1480,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1446,19 +1501,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.01787339871223947</v>
+        <v>-0.05400163337192734</v>
       </c>
       <c r="C10">
-        <v>0.04112807375407749</v>
+        <v>0.04356657014248519</v>
       </c>
       <c r="D10">
-        <v>-0.4345790376449975</v>
+        <v>-1.239519962101999</v>
       </c>
       <c r="E10">
-        <v>0.6646967631606471</v>
+        <v>0.2177211156620189</v>
       </c>
       <c r="H10">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1467,17 +1522,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1488,19 +1543,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.3641954685999594</v>
+        <v>-0.3226046259486922</v>
       </c>
       <c r="C11">
-        <v>0.03617069013451425</v>
+        <v>0.04240354410551972</v>
       </c>
       <c r="D11">
-        <v>-10.0688006572604</v>
+        <v>-7.607963738736131</v>
       </c>
       <c r="E11">
-        <v>2.08870442951955E-17</v>
+        <v>8.998035463107232E-12</v>
       </c>
       <c r="H11">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1509,17 +1564,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1530,19 +1585,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.06083854105233882</v>
+        <v>-0.05593695405384432</v>
       </c>
       <c r="C12">
-        <v>0.02841738849279105</v>
+        <v>0.02825440359472322</v>
       </c>
       <c r="D12">
-        <v>-2.140891344318019</v>
+        <v>-1.979760566041149</v>
       </c>
       <c r="E12">
-        <v>0.03443184599542854</v>
+        <v>0.05016163470314559</v>
       </c>
       <c r="H12">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1551,17 +1606,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1572,19 +1627,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.01970772941623506</v>
+        <v>-0.015322825552719</v>
       </c>
       <c r="C13">
-        <v>0.02143227883390889</v>
+        <v>0.02104744839191481</v>
       </c>
       <c r="D13">
-        <v>-0.9195349486147338</v>
+        <v>-0.7280134516735591</v>
       </c>
       <c r="E13">
-        <v>0.3597745880685864</v>
+        <v>0.4681112321953803</v>
       </c>
       <c r="H13">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1593,17 +1648,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1614,19 +1669,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.0330478491896129</v>
+        <v>0.03766903973271839</v>
       </c>
       <c r="C14">
-        <v>0.03867218541482737</v>
+        <v>0.03752487110711257</v>
       </c>
       <c r="D14">
-        <v>0.8545637862230037</v>
+        <v>1.003841948589092</v>
       </c>
       <c r="E14">
-        <v>0.3946008062179849</v>
+        <v>0.3175995715359192</v>
       </c>
       <c r="H14">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1635,17 +1690,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1656,19 +1711,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.01666109423512238</v>
+        <v>-0.008311566296165557</v>
       </c>
       <c r="C15">
-        <v>0.03731741835331064</v>
+        <v>0.04198795938074956</v>
       </c>
       <c r="D15">
-        <v>-0.4464696372449966</v>
+        <v>-0.1979511845478303</v>
       </c>
       <c r="E15">
-        <v>0.6561124704374393</v>
+        <v>0.8434389243776608</v>
       </c>
       <c r="H15">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1677,17 +1732,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1698,19 +1753,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.02540968829505883</v>
+        <v>0.02658581459768346</v>
       </c>
       <c r="C16">
-        <v>0.01934365583064633</v>
+        <v>0.01940433904159674</v>
       </c>
       <c r="D16">
-        <v>1.313592865667204</v>
+        <v>1.370096375902932</v>
       </c>
       <c r="E16">
-        <v>0.1916440651310459</v>
+        <v>0.173372852226494</v>
       </c>
       <c r="H16">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1719,17 +1774,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1740,19 +1795,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.04335614496980404</v>
+        <v>0.01262016357666339</v>
       </c>
       <c r="C17">
-        <v>0.02437893689486615</v>
+        <v>0.02643596839087383</v>
       </c>
       <c r="D17">
-        <v>1.778426399673491</v>
+        <v>0.4773860896663841</v>
       </c>
       <c r="E17">
-        <v>0.07802314157819919</v>
+        <v>0.6340092768239967</v>
       </c>
       <c r="H17">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1761,17 +1816,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1782,19 +1837,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.05501789431052221</v>
+        <v>0.06430092940325499</v>
       </c>
       <c r="C18">
-        <v>0.05088137365992178</v>
+        <v>0.04901141223842078</v>
       </c>
       <c r="D18">
-        <v>1.081297346220405</v>
+        <v>1.31195830657678</v>
       </c>
       <c r="E18">
-        <v>0.2818671046364752</v>
+        <v>0.1921932151668446</v>
       </c>
       <c r="H18">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1803,40 +1858,40 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B19">
-        <v>-2.879684684485161</v>
+        <v>-1.148124629321888</v>
       </c>
       <c r="C19">
-        <v>1.096631649574163</v>
+        <v>0.2711890694199419</v>
       </c>
       <c r="D19">
-        <v>-2.625936143283282</v>
+        <v>-4.233668531617672</v>
       </c>
       <c r="E19">
-        <v>0.009838370076845113</v>
+        <v>4.702786548957674E-05</v>
       </c>
       <c r="H19">
-        <v>0.6423111997351462</v>
+        <v>0.6521559813389599</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1845,17 +1900,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      country</t>
+          <t>prratio_ln ~ 1 + year_mid + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      country</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1877,22 +1932,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -1902,8 +1992,10 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
-        <v>4.702786548957806E-05</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1912,13 +2004,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.06303705995859937</v>
+      </c>
+      <c r="F2">
+        <v>0.05129342461122213</v>
+      </c>
+      <c r="G2">
+        <v>-1.228950112736437</v>
+      </c>
+      <c r="H2">
+        <v>0.2190905109007946</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>4.702786548957674E-05</v>
       </c>
     </row>
   </sheetData>
@@ -2336,19 +2446,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.1019341118183144</v>
+        <v>0.09803848053883027</v>
       </c>
       <c r="C2">
-        <v>0.03446291468575753</v>
+        <v>0.03451620945444564</v>
       </c>
       <c r="D2">
-        <v>2.957791375099236</v>
+        <v>2.84036057517327</v>
       </c>
       <c r="E2">
-        <v>0.00377410355381709</v>
+        <v>0.005346152484649708</v>
       </c>
       <c r="H2">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2357,17 +2467,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2378,19 +2488,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.05440939053199469</v>
+        <v>-0.06740916276707082</v>
       </c>
       <c r="C3">
-        <v>0.07510922366868994</v>
+        <v>0.07311877689216273</v>
       </c>
       <c r="D3">
-        <v>-0.7244035802047014</v>
+        <v>-0.9219131614644952</v>
       </c>
       <c r="E3">
-        <v>0.4703152106442928</v>
+        <v>0.3585380394057749</v>
       </c>
       <c r="H3">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2399,17 +2509,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2420,19 +2530,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.04209699882826698</v>
+        <v>-0.03938754877562393</v>
       </c>
       <c r="C4">
-        <v>0.0298751415845676</v>
+        <v>0.02968626919092391</v>
       </c>
       <c r="D4">
-        <v>-1.409097885246935</v>
+        <v>-1.326793492382196</v>
       </c>
       <c r="E4">
-        <v>0.1615521700580857</v>
+        <v>0.187251952750318</v>
       </c>
       <c r="H4">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2441,17 +2551,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2462,19 +2572,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1718536704999175</v>
+        <v>0.1639754021674579</v>
       </c>
       <c r="C5">
-        <v>0.04096567678230544</v>
+        <v>0.04129239275640673</v>
       </c>
       <c r="D5">
-        <v>4.195064844483353</v>
+        <v>3.971080172921592</v>
       </c>
       <c r="E5">
-        <v>5.451280566505639E-05</v>
+        <v>0.0001262200645965493</v>
       </c>
       <c r="H5">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2483,17 +2593,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2504,19 +2614,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.07388159122502111</v>
+        <v>0.05988564355749317</v>
       </c>
       <c r="C6">
-        <v>0.04021424565996139</v>
+        <v>0.04093490246923643</v>
       </c>
       <c r="D6">
-        <v>1.837199480247369</v>
+        <v>1.462948240868503</v>
       </c>
       <c r="E6">
-        <v>0.06880812686881221</v>
+        <v>0.1462574717071919</v>
       </c>
       <c r="H6">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2525,17 +2635,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2546,19 +2656,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.06112990035254001</v>
+        <v>-0.06898518960316109</v>
       </c>
       <c r="C7">
-        <v>0.02403787005284125</v>
+        <v>0.02420051588208813</v>
       </c>
       <c r="D7">
-        <v>-2.543066428854187</v>
+        <v>-2.850566902758469</v>
       </c>
       <c r="E7">
-        <v>0.01234065584655042</v>
+        <v>0.005188827455546679</v>
       </c>
       <c r="H7">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2567,17 +2677,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2588,19 +2698,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1662769710471542</v>
+        <v>-0.1641154905264108</v>
       </c>
       <c r="C8">
-        <v>0.05326384590379434</v>
+        <v>0.05453600486327984</v>
       </c>
       <c r="D8">
-        <v>-3.121760515519011</v>
+        <v>-3.009305337599325</v>
       </c>
       <c r="E8">
-        <v>0.002282961869763477</v>
+        <v>0.003229371789525762</v>
       </c>
       <c r="H8">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2609,17 +2719,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2630,19 +2740,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.00198509460596388</v>
+        <v>-0.008011133197379085</v>
       </c>
       <c r="C9">
-        <v>0.03237826677407006</v>
+        <v>0.03233612883113083</v>
       </c>
       <c r="D9">
-        <v>0.06130947711980774</v>
+        <v>-0.2477455863444779</v>
       </c>
       <c r="E9">
-        <v>0.9512210500251815</v>
+        <v>0.8047808739359399</v>
       </c>
       <c r="H9">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2651,17 +2761,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2672,19 +2782,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.03795338794896052</v>
+        <v>-0.02679552080495578</v>
       </c>
       <c r="C10">
-        <v>0.05319105883295117</v>
+        <v>0.05297472048596665</v>
       </c>
       <c r="D10">
-        <v>-0.7135294687055352</v>
+        <v>-0.5058171248313446</v>
       </c>
       <c r="E10">
-        <v>0.4769892797526605</v>
+        <v>0.6139703470835487</v>
       </c>
       <c r="H10">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2693,17 +2803,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2714,19 +2824,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.01623056470922978</v>
+        <v>-0.0475914687068901</v>
       </c>
       <c r="C11">
-        <v>0.04380684431660255</v>
+        <v>0.04371139866598944</v>
       </c>
       <c r="D11">
-        <v>-0.3705029422326704</v>
+        <v>-1.088765634578507</v>
       </c>
       <c r="E11">
-        <v>0.7117013827178338</v>
+        <v>0.2785738415913997</v>
       </c>
       <c r="H11">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2735,17 +2845,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2756,19 +2866,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.3233466871372077</v>
+        <v>-0.2925455070518322</v>
       </c>
       <c r="C12">
-        <v>0.04966782701840689</v>
+        <v>0.05314780984076928</v>
       </c>
       <c r="D12">
-        <v>-6.510183886590718</v>
+        <v>-5.504375588162482</v>
       </c>
       <c r="E12">
-        <v>2.14639678786483E-09</v>
+        <v>2.344674674542442E-07</v>
       </c>
       <c r="H12">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -2777,17 +2887,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2798,19 +2908,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.02495593337782139</v>
+        <v>-0.0227062327588002</v>
       </c>
       <c r="C13">
-        <v>0.03352477476085871</v>
+        <v>0.03234679776327088</v>
       </c>
       <c r="D13">
-        <v>-0.7444027157777738</v>
+        <v>-0.7019623062837663</v>
       </c>
       <c r="E13">
-        <v>0.4581781388820604</v>
+        <v>0.4841460132648839</v>
       </c>
       <c r="H13">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2819,17 +2929,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2840,19 +2950,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.006865409589943234</v>
+        <v>0.01013851568518907</v>
       </c>
       <c r="C14">
-        <v>0.0232036039547054</v>
+        <v>0.02343200197198079</v>
       </c>
       <c r="D14">
-        <v>0.2958768647898343</v>
+        <v>0.4326781679735419</v>
       </c>
       <c r="E14">
-        <v>0.7678671577997536</v>
+        <v>0.6660732542950364</v>
       </c>
       <c r="H14">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2861,17 +2971,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2882,19 +2992,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.01412906651792355</v>
+        <v>0.00374892043578326</v>
       </c>
       <c r="C15">
-        <v>0.04870283624065526</v>
+        <v>0.04508575504820209</v>
       </c>
       <c r="D15">
-        <v>-0.2901076735676669</v>
+        <v>0.08315088505837848</v>
       </c>
       <c r="E15">
-        <v>0.7722655597205258</v>
+        <v>0.9338786853428944</v>
       </c>
       <c r="H15">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2903,17 +3013,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2924,19 +3034,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.06989935365248767</v>
+        <v>0.0726593964391524</v>
       </c>
       <c r="C16">
-        <v>0.04797252730297939</v>
+        <v>0.0459717447378268</v>
       </c>
       <c r="D16">
-        <v>1.457070485593251</v>
+        <v>1.580522924538173</v>
       </c>
       <c r="E16">
-        <v>0.1478702254817372</v>
+        <v>0.1167823130091106</v>
       </c>
       <c r="H16">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2945,17 +3055,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -2966,19 +3076,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.02287642212826797</v>
+        <v>0.02044939013956056</v>
       </c>
       <c r="C17">
-        <v>0.02457180844093276</v>
+        <v>0.02449432494658858</v>
       </c>
       <c r="D17">
-        <v>0.9310027865169033</v>
+        <v>0.8348623684935897</v>
       </c>
       <c r="E17">
-        <v>0.3538368972715425</v>
+        <v>0.4055568006923373</v>
       </c>
       <c r="H17">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2987,17 +3097,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3008,19 +3118,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.1199568508023768</v>
+        <v>0.09980865350453283</v>
       </c>
       <c r="C18">
-        <v>0.02914363001770458</v>
+        <v>0.02801096895158749</v>
       </c>
       <c r="D18">
-        <v>4.116057290375417</v>
+        <v>3.563198891014311</v>
       </c>
       <c r="E18">
-        <v>7.355236497182307E-05</v>
+        <v>0.0005378137114006688</v>
       </c>
       <c r="H18">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3029,17 +3139,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3050,19 +3160,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.05734009692029088</v>
+        <v>0.0874490260619431</v>
       </c>
       <c r="C19">
-        <v>0.05212983747204318</v>
+        <v>0.04949419824951935</v>
       </c>
       <c r="D19">
-        <v>1.099947740121805</v>
+        <v>1.766854078958483</v>
       </c>
       <c r="E19">
-        <v>0.2736926783290706</v>
+        <v>0.0799525844862593</v>
       </c>
       <c r="H19">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3071,40 +3181,40 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B20">
-        <v>-2.260780814058366</v>
+        <v>-1.012175600342418</v>
       </c>
       <c r="C20">
-        <v>0.9847221362674928</v>
+        <v>0.3061176334681326</v>
       </c>
       <c r="D20">
-        <v>-2.295856598316828</v>
+        <v>-3.306492307793785</v>
       </c>
       <c r="E20">
-        <v>0.02352846802468215</v>
+        <v>0.001266925466988191</v>
       </c>
       <c r="H20">
-        <v>0.5658996021951119</v>
+        <v>0.5747254749790025</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3113,17 +3223,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3244,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3145,22 +3255,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -3170,23 +3315,43 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.06740649184275552</v>
+      </c>
+      <c r="F2">
+        <v>0.07540092695402795</v>
+      </c>
+      <c r="G2">
+        <v>-0.8939743125950341</v>
+      </c>
+      <c r="H2">
+        <v>0.3713356351653265</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
         <v>0.001266925466988191</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -3464,7 +3629,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.001 (0.003)</t>
+          <t>0.002 (0.003)</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3641,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.122*** (0.032)</t>
+          <t>0.108** (0.033)</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3653,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.076** (0.028)</t>
+          <t>0.065* (0.029)</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3665,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.001 (0.029)</t>
+          <t>0.003 (0.028)</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3677,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.018 (0.041)</t>
+          <t>-0.054 (0.044)</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3689,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.364*** (0.036)</t>
+          <t>-0.323*** (0.042)</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3701,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.061* (0.028)</t>
+          <t>-0.056 (0.028)</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3713,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.025 (0.019)</t>
+          <t>0.027 (0.019)</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3725,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.043 (0.024)</t>
+          <t>0.013 (0.026)</t>
         </is>
       </c>
     </row>
@@ -3572,19 +3737,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.055 (0.051)</t>
+          <t>0.064 (0.049)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-2.880** (1.097)</t>
+          <t>-1.148*** (0.271)</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3785,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>0.652</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3797,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3830,19 +3995,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.06240645906732189</v>
+        <v>-0.05990812588902553</v>
       </c>
       <c r="C2">
-        <v>0.02933744466412816</v>
+        <v>0.03032095737502168</v>
       </c>
       <c r="D2">
-        <v>-2.127194777247531</v>
+        <v>-1.975799284569348</v>
       </c>
       <c r="E2">
-        <v>0.03557870985601286</v>
+        <v>0.05061495038761549</v>
       </c>
       <c r="H2">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3851,17 +4016,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3872,19 +4037,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1630580683609674</v>
+        <v>0.1386776134302257</v>
       </c>
       <c r="C3">
-        <v>0.0371369330499243</v>
+        <v>0.03844215824974026</v>
       </c>
       <c r="D3">
-        <v>4.390725215293452</v>
+        <v>3.607435683743451</v>
       </c>
       <c r="E3">
-        <v>2.556022445807238E-05</v>
+        <v>0.0004619448879010515</v>
       </c>
       <c r="H3">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3893,17 +4058,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3914,19 +4079,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0965509958259769</v>
+        <v>0.07513383112401724</v>
       </c>
       <c r="C4">
-        <v>0.03680797030193163</v>
+        <v>0.03862720849549992</v>
       </c>
       <c r="D4">
-        <v>2.623100242528452</v>
+        <v>1.94510123952577</v>
       </c>
       <c r="E4">
-        <v>0.009915799637862932</v>
+        <v>0.05424720976920593</v>
       </c>
       <c r="H4">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3935,17 +4100,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3956,19 +4121,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.003792628738719204</v>
+        <v>-0.005760794567148734</v>
       </c>
       <c r="C5">
-        <v>0.02325867631430943</v>
+        <v>0.02298499043055166</v>
       </c>
       <c r="D5">
-        <v>-0.1630629657280137</v>
+        <v>-0.2506328895178256</v>
       </c>
       <c r="E5">
-        <v>0.8707601213256433</v>
+        <v>0.8025530950490125</v>
       </c>
       <c r="H5">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3977,17 +4142,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -3998,19 +4163,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.0201759290682873</v>
+        <v>0.04771651218852441</v>
       </c>
       <c r="C6">
-        <v>0.03904783750406268</v>
+        <v>0.03916235593618038</v>
       </c>
       <c r="D6">
-        <v>0.5166977317550074</v>
+        <v>1.218428029873484</v>
       </c>
       <c r="E6">
-        <v>0.6063769559195313</v>
+        <v>0.2255990976784467</v>
       </c>
       <c r="H6">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4019,17 +4184,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4040,19 +4205,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.04246888672046825</v>
+        <v>0.02782374626812559</v>
       </c>
       <c r="C7">
-        <v>0.02662875792513177</v>
+        <v>0.02708167716106366</v>
       </c>
       <c r="D7">
-        <v>1.59485045603223</v>
+        <v>1.027401150329376</v>
       </c>
       <c r="E7">
-        <v>0.113538859124622</v>
+        <v>0.3064258288992328</v>
       </c>
       <c r="H7">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4061,17 +4226,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4082,19 +4247,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.07111404080233072</v>
+        <v>0.09184666634499045</v>
       </c>
       <c r="C8">
-        <v>0.04328852089442391</v>
+        <v>0.04625969321090101</v>
       </c>
       <c r="D8">
-        <v>1.642792115160744</v>
+        <v>1.985457748849639</v>
       </c>
       <c r="E8">
-        <v>0.1032058529345114</v>
+        <v>0.04951571766247356</v>
       </c>
       <c r="H8">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4103,17 +4268,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4124,19 +4289,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0190683113860329</v>
+        <v>-0.02360596392386918</v>
       </c>
       <c r="C9">
-        <v>0.04125454978250671</v>
+        <v>0.04494706194736318</v>
       </c>
       <c r="D9">
-        <v>0.4622111133574532</v>
+        <v>-0.5251948158817091</v>
       </c>
       <c r="E9">
-        <v>0.6448186453269891</v>
+        <v>0.6004767458581085</v>
       </c>
       <c r="H9">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4145,17 +4310,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4166,19 +4331,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.2968002563141406</v>
+        <v>-0.2427308092863648</v>
       </c>
       <c r="C10">
-        <v>0.05483390433943409</v>
+        <v>0.05202797472848261</v>
       </c>
       <c r="D10">
-        <v>-5.41271426664935</v>
+        <v>-4.665390312675044</v>
       </c>
       <c r="E10">
-        <v>3.526856524621992E-07</v>
+        <v>8.515491135520198E-06</v>
       </c>
       <c r="H10">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4187,17 +4352,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4208,19 +4373,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.08564529048735212</v>
+        <v>-0.08012621328695968</v>
       </c>
       <c r="C11">
-        <v>0.02918171224764191</v>
+        <v>0.02920218109741545</v>
       </c>
       <c r="D11">
-        <v>-2.934895997895835</v>
+        <v>-2.743843448531016</v>
       </c>
       <c r="E11">
-        <v>0.00404237661199616</v>
+        <v>0.007064553057221575</v>
       </c>
       <c r="H11">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -4229,17 +4394,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4250,19 +4415,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.005391030354424405</v>
+        <v>0.01274943384581534</v>
       </c>
       <c r="C12">
-        <v>0.02502579638895569</v>
+        <v>0.0259158733347201</v>
       </c>
       <c r="D12">
-        <v>0.2154189329536605</v>
+        <v>0.4919546287770527</v>
       </c>
       <c r="E12">
-        <v>0.8298290449887242</v>
+        <v>0.6237057650880955</v>
       </c>
       <c r="H12">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4271,17 +4436,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4292,19 +4457,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.1243534365559289</v>
+        <v>0.122702016816378</v>
       </c>
       <c r="C13">
-        <v>0.05205231591740164</v>
+        <v>0.0527397369928783</v>
       </c>
       <c r="D13">
-        <v>2.389008718714016</v>
+        <v>2.326557237722802</v>
       </c>
       <c r="E13">
-        <v>0.0185502366862356</v>
+        <v>0.02177128318187393</v>
       </c>
       <c r="H13">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -4313,17 +4478,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4334,19 +4499,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.01057720219753975</v>
+        <v>0.01576084287417043</v>
       </c>
       <c r="C14">
-        <v>0.04825801534486335</v>
+        <v>0.04865975867164032</v>
       </c>
       <c r="D14">
-        <v>0.2191802153891437</v>
+        <v>0.32389891163509</v>
       </c>
       <c r="E14">
-        <v>0.8269050752800637</v>
+        <v>0.7466132972990722</v>
       </c>
       <c r="H14">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4355,17 +4520,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4376,19 +4541,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.03558728630518013</v>
+        <v>0.0314797033717675</v>
       </c>
       <c r="C15">
-        <v>0.01767337162712379</v>
+        <v>0.01767036694422194</v>
       </c>
       <c r="D15">
-        <v>2.013610478860942</v>
+        <v>1.781496868239122</v>
       </c>
       <c r="E15">
-        <v>0.04642675553740935</v>
+        <v>0.07751770321600394</v>
       </c>
       <c r="H15">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4397,17 +4562,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4418,19 +4583,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.0458619998373196</v>
+        <v>0.01297872531775746</v>
       </c>
       <c r="C16">
-        <v>0.02674397661727321</v>
+        <v>0.02835953257559077</v>
       </c>
       <c r="D16">
-        <v>1.714853422646899</v>
+        <v>0.4576494793474956</v>
       </c>
       <c r="E16">
-        <v>0.08911327612996979</v>
+        <v>0.6480830333512841</v>
       </c>
       <c r="H16">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4439,17 +4604,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4460,19 +4625,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.09623721350224845</v>
+        <v>0.1389539454608043</v>
       </c>
       <c r="C17">
-        <v>0.06912497370736169</v>
+        <v>0.06509619610187579</v>
       </c>
       <c r="D17">
-        <v>1.39222061638194</v>
+        <v>2.134593936077937</v>
       </c>
       <c r="E17">
-        <v>0.166589438341348</v>
+        <v>0.03495511517136365</v>
       </c>
       <c r="H17">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -4481,40 +4646,40 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B18">
-        <v>-2.856726447779597</v>
+        <v>-1.303005326573273</v>
       </c>
       <c r="C18">
-        <v>1.215590568965121</v>
+        <v>0.3299537694051085</v>
       </c>
       <c r="D18">
-        <v>-2.350072895194999</v>
+        <v>-3.949054223331141</v>
       </c>
       <c r="E18">
-        <v>0.02050465716799093</v>
+        <v>0.0001368602003221531</v>
       </c>
       <c r="H18">
-        <v>0.6618989617462047</v>
+        <v>0.6718716247571258</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4523,17 +4688,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      year_mid_fct + country</t>
+          <t>prratio_ln ~ 1 + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      year_mid_fct + country</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4709,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4555,22 +4720,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -4580,8 +4780,10 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
-        <v>0.0001368602003221537</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4590,13 +4792,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.05805916006559827</v>
+      </c>
+      <c r="F2">
+        <v>0.06380114145676187</v>
+      </c>
+      <c r="G2">
+        <v>-0.9100019018459889</v>
+      </c>
+      <c r="H2">
+        <v>0.3628215067963719</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>0.0001368602003221531</v>
       </c>
     </row>
   </sheetData>
@@ -5014,19 +5234,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>-2.898425309719805</v>
+        <v>-0.2168687634943843</v>
       </c>
       <c r="C2">
-        <v>6.348460731702413</v>
+        <v>0.06429417474904796</v>
       </c>
       <c r="D2">
-        <v>-0.4565556017769616</v>
+        <v>-3.37307017845494</v>
       </c>
       <c r="E2">
-        <v>0.6488668551866732</v>
+        <v>0.001018791917010036</v>
       </c>
       <c r="H2">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -5056,19 +5276,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1348764816043596</v>
+        <v>0.1348764815959152</v>
       </c>
       <c r="C3">
-        <v>0.05698345294150444</v>
+        <v>0.0569834529343449</v>
       </c>
       <c r="D3">
-        <v>2.366941184536766</v>
+        <v>2.366941184685964</v>
       </c>
       <c r="E3">
-        <v>0.01963663037585676</v>
+        <v>0.01963663036832522</v>
       </c>
       <c r="H3">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -5098,19 +5318,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.1002180142186456</v>
+        <v>-0.1002180142112939</v>
       </c>
       <c r="C4">
-        <v>0.05655534726332432</v>
+        <v>0.05655534724088072</v>
       </c>
       <c r="D4">
-        <v>-1.77203428266519</v>
+        <v>-1.772034283238419</v>
       </c>
       <c r="E4">
-        <v>0.07908408958592673</v>
+        <v>0.07908408949025318</v>
       </c>
       <c r="H4">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -5140,19 +5360,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.04473716844574081</v>
+        <v>0.04473716844587793</v>
       </c>
       <c r="C5">
-        <v>0.07402753618091264</v>
+        <v>0.07402753619637863</v>
       </c>
       <c r="D5">
-        <v>0.604331452237038</v>
+        <v>0.6043314521126321</v>
       </c>
       <c r="E5">
-        <v>0.5468347614187357</v>
+        <v>0.5468347615011384</v>
       </c>
       <c r="H5">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -5182,19 +5402,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.009334972247178374</v>
+        <v>0.009334972247263335</v>
       </c>
       <c r="C6">
-        <v>0.03718963336625804</v>
+        <v>0.03718963336660558</v>
       </c>
       <c r="D6">
-        <v>0.2510100638864578</v>
+        <v>0.2510100638863967</v>
       </c>
       <c r="E6">
-        <v>0.8022621953203117</v>
+        <v>0.8022621953203589</v>
       </c>
       <c r="H6">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -5224,19 +5444,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.1096937550754127</v>
+        <v>0.1096937550749223</v>
       </c>
       <c r="C7">
-        <v>0.03934796677007042</v>
+        <v>0.03934796676183381</v>
       </c>
       <c r="D7">
-        <v>2.787787122938459</v>
+        <v>2.787787123509555</v>
       </c>
       <c r="E7">
-        <v>0.00622788417198812</v>
+        <v>0.006227884161728476</v>
       </c>
       <c r="H7">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -5266,19 +5486,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.2132327959589587</v>
+        <v>0.2132327959514105</v>
       </c>
       <c r="C8">
-        <v>0.06789999656867488</v>
+        <v>0.06789999655255154</v>
       </c>
       <c r="D8">
-        <v>3.140394797270608</v>
+        <v>3.14039479790515</v>
       </c>
       <c r="E8">
-        <v>0.002153611038758015</v>
+        <v>0.002153611034471615</v>
       </c>
       <c r="H8">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -5308,19 +5528,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.09773557787920766</v>
+        <v>0.09773557788524578</v>
       </c>
       <c r="C9">
-        <v>0.04582901227979592</v>
+        <v>0.04582901228016507</v>
       </c>
       <c r="D9">
-        <v>2.13261366582616</v>
+        <v>2.132613665940735</v>
       </c>
       <c r="E9">
-        <v>0.03512107695831212</v>
+        <v>0.03512107694869011</v>
       </c>
       <c r="H9">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -5350,19 +5570,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.06584204500359175</v>
+        <v>0.06584204499739488</v>
       </c>
       <c r="C10">
-        <v>0.06388086656471396</v>
+        <v>0.06388086658342092</v>
       </c>
       <c r="D10">
-        <v>1.03070056097143</v>
+        <v>1.030700560572592</v>
       </c>
       <c r="E10">
-        <v>0.3048823034167024</v>
+        <v>0.3048823036029698</v>
       </c>
       <c r="H10">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -5392,19 +5612,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.01774623424341277</v>
+        <v>0.01774623424468149</v>
       </c>
       <c r="C11">
-        <v>0.1111245065828685</v>
+        <v>0.1111245065938217</v>
       </c>
       <c r="D11">
-        <v>0.1596968552582857</v>
+        <v>0.159696855253962</v>
       </c>
       <c r="E11">
-        <v>0.8734049817046999</v>
+        <v>0.873404981708098</v>
       </c>
       <c r="H11">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -5434,19 +5654,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.1867216506526501</v>
+        <v>0.1867216506526186</v>
       </c>
       <c r="C12">
-        <v>0.039515222379429</v>
+        <v>0.03951522238595619</v>
       </c>
       <c r="D12">
-        <v>4.725309372163737</v>
+        <v>4.725309371382406</v>
       </c>
       <c r="E12">
-        <v>6.664162564124454E-06</v>
+        <v>6.664162585508429E-06</v>
       </c>
       <c r="H12">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -5476,19 +5696,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.1110418290424146</v>
+        <v>0.1110418290444323</v>
       </c>
       <c r="C13">
-        <v>0.03967054304625545</v>
+        <v>0.03967054304401902</v>
       </c>
       <c r="D13">
-        <v>2.799100302532812</v>
+        <v>2.799100302741473</v>
       </c>
       <c r="E13">
-        <v>0.006027643538099593</v>
+        <v>0.006027643534461165</v>
       </c>
       <c r="H13">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -5518,19 +5738,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.2513889319627504</v>
+        <v>0.2513889319647236</v>
       </c>
       <c r="C14">
-        <v>0.04632136116765245</v>
+        <v>0.04632136116635751</v>
       </c>
       <c r="D14">
-        <v>5.427062712015089</v>
+        <v>5.427062712209405</v>
       </c>
       <c r="E14">
-        <v>3.309302302595933E-07</v>
+        <v>3.309302299740479E-07</v>
       </c>
       <c r="H14">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -5560,19 +5780,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.001331444828546066</v>
+        <v>0.001331444827252719</v>
       </c>
       <c r="C15">
-        <v>0.003157199753453933</v>
+        <v>0.003157199750530711</v>
       </c>
       <c r="D15">
-        <v>0.4217170063723348</v>
+        <v>0.4217170063531486</v>
       </c>
       <c r="E15">
-        <v>0.6740327711730392</v>
+        <v>0.6740327711870042</v>
       </c>
       <c r="H15">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5602,19 +5822,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.06489038894349759</v>
+        <v>-0.06489038894039725</v>
       </c>
       <c r="C16">
-        <v>0.02941536060414877</v>
+        <v>0.02941536061022726</v>
       </c>
       <c r="D16">
-        <v>-2.206003516895366</v>
+        <v>-2.206003516334112</v>
       </c>
       <c r="E16">
-        <v>0.02940720419704854</v>
+        <v>0.02940720423744737</v>
       </c>
       <c r="H16">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5644,19 +5864,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.1418417527551345</v>
+        <v>0.141841752756022</v>
       </c>
       <c r="C17">
-        <v>0.04128813728875738</v>
+        <v>0.04128813728058874</v>
       </c>
       <c r="D17">
-        <v>3.435411768836507</v>
+        <v>3.43541176953768</v>
       </c>
       <c r="E17">
-        <v>0.0008284459412102468</v>
+        <v>0.0008284459392709811</v>
       </c>
       <c r="H17">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5686,19 +5906,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.04953373180222685</v>
+        <v>0.04953373180201844</v>
       </c>
       <c r="C18">
-        <v>0.04104657804736105</v>
+        <v>0.04104657804910194</v>
       </c>
       <c r="D18">
-        <v>1.206768850379513</v>
+        <v>1.206768850323254</v>
       </c>
       <c r="E18">
-        <v>0.2300414027120305</v>
+        <v>0.230041402733617</v>
       </c>
       <c r="H18">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5728,19 +5948,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.04453313983994608</v>
+        <v>-0.04453313984119805</v>
       </c>
       <c r="C19">
-        <v>0.02955161793399527</v>
+        <v>0.02955161792787906</v>
       </c>
       <c r="D19">
-        <v>-1.50696113963752</v>
+        <v>-1.506961139991776</v>
       </c>
       <c r="E19">
-        <v>0.1346111796640688</v>
+        <v>0.1346111795733411</v>
       </c>
       <c r="H19">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5770,19 +5990,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.09085106868421931</v>
+        <v>-0.09085106868901181</v>
       </c>
       <c r="C20">
-        <v>0.03702998577553872</v>
+        <v>0.03702998577759394</v>
       </c>
       <c r="D20">
-        <v>-2.45344595147627</v>
+        <v>-2.453445951469522</v>
       </c>
       <c r="E20">
-        <v>0.01567678829135315</v>
+        <v>0.01567678829163202</v>
       </c>
       <c r="H20">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5812,19 +6032,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.0159685364795785</v>
+        <v>0.01596853648052965</v>
       </c>
       <c r="C21">
-        <v>0.02350297413106963</v>
+        <v>0.02350297412050696</v>
       </c>
       <c r="D21">
-        <v>0.6794262032765026</v>
+        <v>0.6794262036223185</v>
       </c>
       <c r="E21">
-        <v>0.4982572354162376</v>
+        <v>0.4982572351980128</v>
       </c>
       <c r="H21">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -5854,19 +6074,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.01182758180669069</v>
+        <v>0.01182758181010015</v>
       </c>
       <c r="C22">
-        <v>0.0473408614537093</v>
+        <v>0.04734086145239545</v>
       </c>
       <c r="D22">
-        <v>0.2498387533200236</v>
+        <v>0.2498387533989768</v>
       </c>
       <c r="E22">
-        <v>0.8031656716129033</v>
+        <v>0.8031656715519947</v>
       </c>
       <c r="H22">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -5896,19 +6116,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.05012161730367316</v>
+        <v>-0.05012161730435691</v>
       </c>
       <c r="C23">
-        <v>0.04057732879618297</v>
+        <v>0.0405773287980707</v>
       </c>
       <c r="D23">
-        <v>-1.235212341241842</v>
+        <v>-1.235212341201228</v>
       </c>
       <c r="E23">
-        <v>0.2193135369255609</v>
+        <v>0.2193135369406147</v>
       </c>
       <c r="H23">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -5938,19 +6158,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.3006584463648106</v>
+        <v>-0.3006584463608996</v>
       </c>
       <c r="C24">
-        <v>0.04125371032814113</v>
+        <v>0.04125371033402341</v>
       </c>
       <c r="D24">
-        <v>-7.288034069500825</v>
+        <v>-7.288034068366836</v>
       </c>
       <c r="E24">
-        <v>4.57196357388022E-11</v>
+        <v>4.571963600043293E-11</v>
       </c>
       <c r="H24">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -5980,19 +6200,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.02708008969329937</v>
+        <v>-0.02708008968886765</v>
       </c>
       <c r="C25">
-        <v>0.03351206229993114</v>
+        <v>0.03351206227940839</v>
       </c>
       <c r="D25">
-        <v>-0.8080699257161208</v>
+        <v>-0.8080699260787395</v>
       </c>
       <c r="E25">
-        <v>0.4207482078943345</v>
+        <v>0.4207482076864635</v>
       </c>
       <c r="H25">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -6022,19 +6242,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.00317715578946622</v>
+        <v>-0.003177155792316006</v>
       </c>
       <c r="C26">
-        <v>0.01879490082722259</v>
+        <v>0.01879490081609396</v>
       </c>
       <c r="D26">
-        <v>-0.1690434984825469</v>
+        <v>-0.1690434987342645</v>
       </c>
       <c r="E26">
-        <v>0.8660646554723905</v>
+        <v>0.8660646552748603</v>
       </c>
       <c r="H26">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -6064,19 +6284,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.07164749944971929</v>
+        <v>-0.07164749944819568</v>
       </c>
       <c r="C27">
-        <v>0.03550291341282332</v>
+        <v>0.03550291340170458</v>
       </c>
       <c r="D27">
-        <v>-2.018073801904969</v>
+        <v>-2.018073802494071</v>
       </c>
       <c r="E27">
-        <v>0.04595244926733463</v>
+        <v>0.04595244920500621</v>
       </c>
       <c r="H27">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -6106,19 +6326,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.07286059305511931</v>
+        <v>0.07286059305608676</v>
       </c>
       <c r="C28">
-        <v>0.0383924888221003</v>
+        <v>0.0383924888152834</v>
       </c>
       <c r="D28">
-        <v>1.897782490547415</v>
+        <v>1.897782490909581</v>
       </c>
       <c r="E28">
-        <v>0.0602764233784781</v>
+        <v>0.06027642333026045</v>
       </c>
       <c r="H28">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -6148,19 +6368,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.01343670591362263</v>
+        <v>-0.0134367059127899</v>
       </c>
       <c r="C29">
-        <v>0.02687014122778927</v>
+        <v>0.02687014123060992</v>
       </c>
       <c r="D29">
-        <v>-0.500060859364829</v>
+        <v>-0.500060859281345</v>
       </c>
       <c r="E29">
-        <v>0.6180046507242376</v>
+        <v>0.6180046507828327</v>
       </c>
       <c r="H29">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -6190,19 +6410,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.0673901876027201</v>
+        <v>0.06739018760892072</v>
       </c>
       <c r="C30">
-        <v>0.027286598905266</v>
+        <v>0.02728659890082253</v>
       </c>
       <c r="D30">
-        <v>2.469717381659998</v>
+        <v>2.469717382289418</v>
       </c>
       <c r="E30">
-        <v>0.01501704998230929</v>
+        <v>0.01501704995727564</v>
       </c>
       <c r="H30">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -6232,19 +6452,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.09040592958492656</v>
+        <v>0.09040592959152012</v>
       </c>
       <c r="C31">
-        <v>0.04037595299321331</v>
+        <v>0.04037595298792698</v>
       </c>
       <c r="D31">
-        <v>2.239103299930101</v>
+        <v>2.239103300386565</v>
       </c>
       <c r="E31">
-        <v>0.02710724900654736</v>
+        <v>0.02710724897594651</v>
       </c>
       <c r="H31">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -6274,19 +6494,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>-2.323569925583837</v>
+        <v>-2.323569925499494</v>
       </c>
       <c r="C32">
-        <v>0.9157010588151936</v>
+        <v>0.9157010586520689</v>
       </c>
       <c r="D32">
-        <v>-2.537476508534625</v>
+        <v>-2.537476508894549</v>
       </c>
       <c r="E32">
-        <v>0.01252842783834732</v>
+        <v>0.01252842782617498</v>
       </c>
       <c r="H32">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -6316,19 +6536,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.05259392300451284</v>
+        <v>0.05259392300934265</v>
       </c>
       <c r="C33">
-        <v>0.08763625726142714</v>
+        <v>0.08763625727507801</v>
       </c>
       <c r="D33">
-        <v>0.600138854031845</v>
+        <v>0.6001388539934749</v>
       </c>
       <c r="E33">
-        <v>0.549615345571606</v>
+        <v>0.5496153455970857</v>
       </c>
       <c r="H33">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -6358,19 +6578,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.2309013712291355</v>
+        <v>0.2309013712270108</v>
       </c>
       <c r="C34">
-        <v>0.1543533503681649</v>
+        <v>0.1543533503587796</v>
       </c>
       <c r="D34">
-        <v>1.495927174100125</v>
+        <v>1.495927174177319</v>
       </c>
       <c r="E34">
-        <v>0.137460364735143</v>
+        <v>0.1374603647150464</v>
       </c>
       <c r="H34">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -6400,19 +6620,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.05006258420236421</v>
+        <v>0.05006258420754498</v>
       </c>
       <c r="C35">
-        <v>0.05622960339035022</v>
+        <v>0.05622960339089593</v>
       </c>
       <c r="D35">
-        <v>0.8903243342270425</v>
+        <v>0.8903243343105378</v>
       </c>
       <c r="E35">
-        <v>0.3751834042950617</v>
+        <v>0.3751834042504351</v>
       </c>
       <c r="H35">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -6442,19 +6662,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.1175405353885464</v>
+        <v>-0.1175405353817006</v>
       </c>
       <c r="C36">
-        <v>0.09016766739712445</v>
+        <v>0.09016766740396177</v>
       </c>
       <c r="D36">
-        <v>-1.303577421725505</v>
+        <v>-1.303577421550733</v>
       </c>
       <c r="E36">
-        <v>0.1950273007280862</v>
+        <v>0.1950273007875093</v>
       </c>
       <c r="H36">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -6484,19 +6704,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.06060333191893207</v>
+        <v>-0.06060333190705022</v>
       </c>
       <c r="C37">
-        <v>0.1313439162517754</v>
+        <v>0.1313439162340391</v>
       </c>
       <c r="D37">
-        <v>-0.4614095090842312</v>
+        <v>-0.4614095090560749</v>
       </c>
       <c r="E37">
-        <v>0.645391787994066</v>
+        <v>0.6453917880142013</v>
       </c>
       <c r="H37">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -6526,19 +6746,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.1026073796594088</v>
+        <v>-0.1026073796594428</v>
       </c>
       <c r="C38">
-        <v>0.1385749817057546</v>
+        <v>0.1385749817757255</v>
       </c>
       <c r="D38">
-        <v>-0.7404466404858114</v>
+        <v>-0.7404466401121819</v>
       </c>
       <c r="E38">
-        <v>0.4605647829916808</v>
+        <v>0.4605647832174183</v>
       </c>
       <c r="H38">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -6568,19 +6788,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.1168644199668819</v>
+        <v>-0.1168644199674946</v>
       </c>
       <c r="C39">
-        <v>0.1315069015594697</v>
+        <v>0.1315069015639624</v>
       </c>
       <c r="D39">
-        <v>-0.8886561737904969</v>
+        <v>-0.8886561737647969</v>
       </c>
       <c r="E39">
-        <v>0.3760756721841725</v>
+        <v>0.3760756721979295</v>
       </c>
       <c r="H39">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -6610,19 +6830,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.198469693078115</v>
+        <v>-1.19846969309422</v>
       </c>
       <c r="C40">
-        <v>0.1163299966176032</v>
+        <v>0.1163299965749943</v>
       </c>
       <c r="D40">
-        <v>-10.30232724082072</v>
+        <v>-10.30232724473266</v>
       </c>
       <c r="E40">
-        <v>5.974733853270781E-18</v>
+        <v>5.974733727973938E-18</v>
       </c>
       <c r="H40">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -6652,19 +6872,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.02686474227598726</v>
+        <v>0.02686474228133614</v>
       </c>
       <c r="C41">
-        <v>0.06087154098611953</v>
+        <v>0.06087154099456214</v>
       </c>
       <c r="D41">
-        <v>0.4413350120726071</v>
+        <v>0.4413350120992675</v>
       </c>
       <c r="E41">
-        <v>0.6598138006679339</v>
+        <v>0.6598138006486937</v>
       </c>
       <c r="H41">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -6694,19 +6914,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.09710303736835325</v>
+        <v>-0.09710303736429329</v>
       </c>
       <c r="C42">
-        <v>0.07088679394217799</v>
+        <v>0.07088679394157545</v>
       </c>
       <c r="D42">
-        <v>-1.36983254522076</v>
+        <v>-1.36983254517513</v>
       </c>
       <c r="E42">
-        <v>0.1734549880252752</v>
+        <v>0.1734549880394832</v>
       </c>
       <c r="H42">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -6736,19 +6956,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.03651591957129686</v>
+        <v>0.03651591956561888</v>
       </c>
       <c r="C43">
-        <v>0.09273370818573066</v>
+        <v>0.09273370819880622</v>
       </c>
       <c r="D43">
-        <v>0.3937718040797136</v>
+        <v>0.3937718039629624</v>
       </c>
       <c r="E43">
-        <v>0.6944915662175114</v>
+        <v>0.6944915663034714</v>
       </c>
       <c r="H43">
-        <v>0.5351241400194859</v>
+        <v>0.5351241400194863</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -6778,7 +6998,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6789,22 +7009,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -6814,8 +7069,10 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
-        <v>0.000550498158524658</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6824,13 +7081,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>peese</t>
         </is>
+      </c>
+      <c r="E2">
+        <v>-0.06940486016856232</v>
+      </c>
+      <c r="F2">
+        <v>0.01081591752391697</v>
+      </c>
+      <c r="G2">
+        <v>-6.416918399672435</v>
+      </c>
+      <c r="H2">
+        <v>1.390604101154682E-10</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>0.0005504981579581781</v>
       </c>
     </row>
   </sheetData>
@@ -7258,19 +7533,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>23.01652449412381</v>
+        <v>0.08107657234509681</v>
       </c>
       <c r="C2">
-        <v>13.2671772616149</v>
+        <v>0.0336340113600497</v>
       </c>
       <c r="D2">
-        <v>1.734847137432624</v>
+        <v>2.410553159335587</v>
       </c>
       <c r="E2">
-        <v>0.08549447114377341</v>
+        <v>0.0175413522183467</v>
       </c>
       <c r="H2">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7279,17 +7554,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7300,19 +7575,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>-72.29079732473474</v>
+        <v>-0.2849934764800142</v>
       </c>
       <c r="C3">
-        <v>25.10109981261331</v>
+        <v>0.07007845022655101</v>
       </c>
       <c r="D3">
-        <v>-2.879985254208208</v>
+        <v>-4.066777669293222</v>
       </c>
       <c r="E3">
-        <v>0.004758778854512331</v>
+        <v>8.849760505257059E-05</v>
       </c>
       <c r="H3">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -7321,17 +7596,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7342,19 +7617,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.005497312332951809</v>
+        <v>0.007588143336562234</v>
       </c>
       <c r="C4">
-        <v>0.003958796166958127</v>
+        <v>0.004115808510193612</v>
       </c>
       <c r="D4">
-        <v>1.388632326876241</v>
+        <v>1.843658012215267</v>
       </c>
       <c r="E4">
-        <v>0.1676756796734578</v>
+        <v>0.06785314917534446</v>
       </c>
       <c r="H4">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7363,17 +7638,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7384,19 +7659,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.01951363299746944</v>
+        <v>-0.01197026289495886</v>
       </c>
       <c r="C5">
-        <v>0.03279339695690529</v>
+        <v>0.03107650059199781</v>
       </c>
       <c r="D5">
-        <v>-0.5950476256885753</v>
+        <v>-0.3851869633623162</v>
       </c>
       <c r="E5">
-        <v>0.553001381072775</v>
+        <v>0.7008229867298407</v>
       </c>
       <c r="H5">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7405,17 +7680,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7426,19 +7701,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1355856130486224</v>
+        <v>0.1215600842838549</v>
       </c>
       <c r="C6">
-        <v>0.04286875175729323</v>
+        <v>0.04266541738857474</v>
       </c>
       <c r="D6">
-        <v>3.162807581061776</v>
+        <v>2.849147898325897</v>
       </c>
       <c r="E6">
-        <v>0.002007057576331684</v>
+        <v>0.005210443963328909</v>
       </c>
       <c r="H6">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7447,17 +7722,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7468,19 +7743,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.05029269210886866</v>
+        <v>0.03816226866913571</v>
       </c>
       <c r="C7">
-        <v>0.04215710528333221</v>
+        <v>0.04176098976469796</v>
       </c>
       <c r="D7">
-        <v>1.192982577215828</v>
+        <v>0.9138257709925166</v>
       </c>
       <c r="E7">
-        <v>0.2353750721538568</v>
+        <v>0.3627541304572822</v>
       </c>
       <c r="H7">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7489,17 +7764,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7510,19 +7785,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.04078110427790804</v>
+        <v>-0.05295287283062244</v>
       </c>
       <c r="C8">
-        <v>0.02887833237191259</v>
+        <v>0.02789336604010497</v>
       </c>
       <c r="D8">
-        <v>-1.412169641678209</v>
+        <v>-1.898403826719479</v>
       </c>
       <c r="E8">
-        <v>0.160648026383345</v>
+        <v>0.060193748350419</v>
       </c>
       <c r="H8">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7531,17 +7806,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7552,19 +7827,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.06427815346748389</v>
+        <v>-0.068648852156122</v>
       </c>
       <c r="C9">
-        <v>0.02952442131044217</v>
+        <v>0.0291039661150934</v>
       </c>
       <c r="D9">
-        <v>-2.177118148789932</v>
+        <v>-2.358745604796472</v>
       </c>
       <c r="E9">
-        <v>0.03155149550296799</v>
+        <v>0.02005422095018198</v>
       </c>
       <c r="H9">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7573,17 +7848,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7594,19 +7869,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.003041480585617595</v>
+        <v>-0.01124557589580014</v>
       </c>
       <c r="C10">
-        <v>0.02202317502687595</v>
+        <v>0.02254577058485848</v>
       </c>
       <c r="D10">
-        <v>-0.138103637731886</v>
+        <v>-0.4987887130969282</v>
       </c>
       <c r="E10">
-        <v>0.8904043086411656</v>
+        <v>0.6188978229352502</v>
       </c>
       <c r="H10">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -7615,17 +7890,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7636,19 +7911,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.04285023863737081</v>
+        <v>0.03817811031276872</v>
       </c>
       <c r="C11">
-        <v>0.04719958960530039</v>
+        <v>0.04497691165597943</v>
       </c>
       <c r="D11">
-        <v>0.9078519325210158</v>
+        <v>0.8488379683511051</v>
       </c>
       <c r="E11">
-        <v>0.3658885056620973</v>
+        <v>0.3977660936920998</v>
       </c>
       <c r="H11">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -7657,17 +7932,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7678,19 +7953,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.07378216759641987</v>
+        <v>-0.107547353217489</v>
       </c>
       <c r="C12">
-        <v>0.04229598965507104</v>
+        <v>0.04328349870231235</v>
       </c>
       <c r="D12">
-        <v>-1.744424665272581</v>
+        <v>-2.484719499159698</v>
       </c>
       <c r="E12">
-        <v>0.08380409662236706</v>
+        <v>0.0144308529074438</v>
       </c>
       <c r="H12">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -7699,17 +7974,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7720,19 +7995,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.2579723087912251</v>
+        <v>-0.235008079425455</v>
       </c>
       <c r="C13">
-        <v>0.04237022809094913</v>
+        <v>0.03939659048738697</v>
       </c>
       <c r="D13">
-        <v>-6.088527733140328</v>
+        <v>-5.965188269291834</v>
       </c>
       <c r="E13">
-        <v>1.605203394862746E-08</v>
+        <v>2.858432948569704E-08</v>
       </c>
       <c r="H13">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7741,17 +8016,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7762,19 +8037,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.002181732464027419</v>
+        <v>-0.002795977489849676</v>
       </c>
       <c r="C14">
-        <v>0.03117239488362391</v>
+        <v>0.03030740970242016</v>
       </c>
       <c r="D14">
-        <v>0.06998924760745828</v>
+        <v>-0.09225392461126121</v>
       </c>
       <c r="E14">
-        <v>0.9443259275575111</v>
+        <v>0.9266596491848429</v>
       </c>
       <c r="H14">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7783,17 +8058,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7804,19 +8079,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.0174598808900055</v>
+        <v>-0.01539929485215695</v>
       </c>
       <c r="C15">
-        <v>0.02060077375056066</v>
+        <v>0.02013754031259253</v>
       </c>
       <c r="D15">
-        <v>-0.8475351994742586</v>
+        <v>-0.7647058485354028</v>
       </c>
       <c r="E15">
-        <v>0.3984884368004012</v>
+        <v>0.4460407579041307</v>
       </c>
       <c r="H15">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -7825,17 +8100,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7846,19 +8121,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.07297779929003134</v>
+        <v>-0.05564270683422152</v>
       </c>
       <c r="C16">
-        <v>0.03211760331708748</v>
+        <v>0.02855430873311948</v>
       </c>
       <c r="D16">
-        <v>-2.272205636564577</v>
+        <v>-1.948662366660022</v>
       </c>
       <c r="E16">
-        <v>0.02496602664099446</v>
+        <v>0.0538148530935434</v>
       </c>
       <c r="H16">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -7867,17 +8142,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7888,19 +8163,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.04871362430600179</v>
+        <v>0.04858145102724822</v>
       </c>
       <c r="C17">
-        <v>0.0369212589535322</v>
+        <v>0.03683058290517666</v>
       </c>
       <c r="D17">
-        <v>1.319392287443693</v>
+        <v>1.319051918138932</v>
       </c>
       <c r="E17">
-        <v>0.1897051142651486</v>
+        <v>0.1898185055985839</v>
       </c>
       <c r="H17">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -7909,17 +8184,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7930,19 +8205,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.0001884347425900046</v>
+        <v>0.002948093603673286</v>
       </c>
       <c r="C18">
-        <v>0.02360183229299149</v>
+        <v>0.02332775835569554</v>
       </c>
       <c r="D18">
-        <v>-0.007983903124587487</v>
+        <v>0.1263770636990287</v>
       </c>
       <c r="E18">
-        <v>0.9936439127590849</v>
+        <v>0.8996580478741554</v>
       </c>
       <c r="H18">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -7951,17 +8226,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -7972,19 +8247,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.07002337999231756</v>
+        <v>0.04841584402494523</v>
       </c>
       <c r="C19">
-        <v>0.02916371398392491</v>
+        <v>0.02857608701306939</v>
       </c>
       <c r="D19">
-        <v>2.401044669101973</v>
+        <v>1.69427829649322</v>
       </c>
       <c r="E19">
-        <v>0.0179804490539726</v>
+        <v>0.09296688196434078</v>
       </c>
       <c r="H19">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -7993,17 +8268,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -8014,19 +8289,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.09058772054447317</v>
+        <v>0.1034945842978335</v>
       </c>
       <c r="C20">
-        <v>0.04430009243447908</v>
+        <v>0.03983423789415914</v>
       </c>
       <c r="D20">
-        <v>2.044865271521829</v>
+        <v>2.598131400751835</v>
       </c>
       <c r="E20">
-        <v>0.0431914661049044</v>
+        <v>0.01062163918254679</v>
       </c>
       <c r="H20">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -8035,40 +8310,40 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B21">
-        <v>-2.904712607532659</v>
+        <v>-1.162017397902721</v>
       </c>
       <c r="C21">
-        <v>1.076777360033365</v>
+        <v>0.2852344302822338</v>
       </c>
       <c r="D21">
-        <v>-2.697598143633567</v>
+        <v>-4.073902988334641</v>
       </c>
       <c r="E21">
-        <v>0.008054371883362688</v>
+        <v>8.616974453637638E-05</v>
       </c>
       <c r="H21">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -8077,17 +8352,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -8098,19 +8373,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.0113833540734205</v>
+        <v>-0.01348711052174832</v>
       </c>
       <c r="C22">
-        <v>0.006583973832405446</v>
+        <v>0.006518759051509814</v>
       </c>
       <c r="D22">
-        <v>-1.72894886328271</v>
+        <v>-2.068969019283596</v>
       </c>
       <c r="E22">
-        <v>0.08654930555209138</v>
+        <v>0.04083008380771421</v>
       </c>
       <c r="H22">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8119,17 +8394,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -8140,19 +8415,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.03575613204256456</v>
+        <v>0.03562503874512638</v>
       </c>
       <c r="C23">
-        <v>0.0124382760766988</v>
+        <v>0.01236122134959595</v>
       </c>
       <c r="D23">
-        <v>2.874685512854002</v>
+        <v>2.881999904183485</v>
       </c>
       <c r="E23">
-        <v>0.004833753921314693</v>
+        <v>0.004730558606526212</v>
       </c>
       <c r="H23">
-        <v>0.5436578182572214</v>
+        <v>0.5566006388063065</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8161,17 +8436,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:year_mid | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:year_mid | treatment_group</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8480,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.102** (0.034)</t>
+          <t>0.098** (0.035)</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.054 (0.075)</t>
+          <t>-0.067 (0.073)</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.172*** (0.041)</t>
+          <t>0.164*** (0.041)</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8516,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.074 (0.040)</t>
+          <t>0.060 (0.041)</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8528,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.166** (0.053)</t>
+          <t>-0.164** (0.055)</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.016 (0.044)</t>
+          <t>-0.048 (0.044)</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8552,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.323*** (0.050)</t>
+          <t>-0.293*** (0.053)</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8564,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.025 (0.034)</t>
+          <t>-0.023 (0.032)</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8576,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.023 (0.025)</t>
+          <t>0.020 (0.024)</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8588,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.120*** (0.029)</t>
+          <t>0.100*** (0.028)</t>
         </is>
       </c>
     </row>
@@ -8325,19 +8600,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.057 (0.052)</t>
+          <t>0.087 (0.049)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-2.261* (0.985)</t>
+          <t>-1.012** (0.306)</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8648,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>0.575</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8660,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8695,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8431,22 +8706,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -8456,8 +8766,10 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
-        <v>8.616974454625951E-05</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8466,13 +8778,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.06259054330120233</v>
+      </c>
+      <c r="F2">
+        <v>0.0664416181147264</v>
+      </c>
+      <c r="G2">
+        <v>-0.942038214558918</v>
+      </c>
+      <c r="H2">
+        <v>0.3461730752439474</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>8.616974453637638E-05</v>
       </c>
     </row>
   </sheetData>
@@ -8910,19 +9240,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.1072283144498822</v>
+        <v>0.1031236272823757</v>
       </c>
       <c r="C2">
-        <v>0.0346524738585171</v>
+        <v>0.03441633281960033</v>
       </c>
       <c r="D2">
-        <v>3.094391323623404</v>
+        <v>2.996357218618193</v>
       </c>
       <c r="E2">
-        <v>0.002486066026118609</v>
+        <v>0.003359006110966127</v>
       </c>
       <c r="H2">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -8931,17 +9261,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -8952,19 +9282,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.07356288642879472</v>
+        <v>-0.07736736085893262</v>
       </c>
       <c r="C3">
-        <v>0.06510660792635499</v>
+        <v>0.06449921267630662</v>
       </c>
       <c r="D3">
-        <v>-1.129883567456087</v>
+        <v>-1.199508608689623</v>
       </c>
       <c r="E3">
-        <v>0.2609179731906618</v>
+        <v>0.2328393085739418</v>
       </c>
       <c r="H3">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -8973,17 +9303,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -8994,19 +9324,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.05922326187430239</v>
+        <v>-0.05552874050319765</v>
       </c>
       <c r="C4">
-        <v>0.02976595091758165</v>
+        <v>0.02963339671801779</v>
       </c>
       <c r="D4">
-        <v>-1.989631106974694</v>
+        <v>-1.873856751272624</v>
       </c>
       <c r="E4">
-        <v>0.04904706215011013</v>
+        <v>0.06353329316708936</v>
       </c>
       <c r="H4">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -9015,17 +9345,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9036,19 +9366,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1539943397987035</v>
+        <v>0.1448418270841254</v>
       </c>
       <c r="C5">
-        <v>0.04552639378033294</v>
+        <v>0.04747442773645486</v>
       </c>
       <c r="D5">
-        <v>3.382528836826691</v>
+        <v>3.050944139615267</v>
       </c>
       <c r="E5">
-        <v>0.0009874852781356443</v>
+        <v>0.002843154045150574</v>
       </c>
       <c r="H5">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -9057,17 +9387,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9078,19 +9408,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.08010633532158265</v>
+        <v>0.06786334707228375</v>
       </c>
       <c r="C6">
-        <v>0.05105959678450322</v>
+        <v>0.05296041647471031</v>
       </c>
       <c r="D6">
-        <v>1.568879120994062</v>
+        <v>1.28139753403733</v>
       </c>
       <c r="E6">
-        <v>0.119472179372455</v>
+        <v>0.2026773382420631</v>
       </c>
       <c r="H6">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -9099,17 +9429,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9120,19 +9450,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.05146724206594888</v>
+        <v>-0.05943065742328836</v>
       </c>
       <c r="C7">
-        <v>0.02397540410493437</v>
+        <v>0.02331991986108211</v>
       </c>
       <c r="D7">
-        <v>-2.1466683873477</v>
+        <v>-2.548493209981838</v>
       </c>
       <c r="E7">
-        <v>0.03395779328783951</v>
+        <v>0.01216078441174359</v>
       </c>
       <c r="H7">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -9141,17 +9471,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9162,19 +9492,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1154471956666258</v>
+        <v>-0.1165793508006502</v>
       </c>
       <c r="C8">
-        <v>0.0342690299763025</v>
+        <v>0.03474971867466549</v>
       </c>
       <c r="D8">
-        <v>-3.368849242200878</v>
+        <v>-3.354828621552069</v>
       </c>
       <c r="E8">
-        <v>0.001033060827159973</v>
+        <v>0.001081814129495608</v>
       </c>
       <c r="H8">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -9183,17 +9513,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9204,19 +9534,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.02202143305299331</v>
+        <v>0.01635153106311299</v>
       </c>
       <c r="C9">
-        <v>0.02358164033435192</v>
+        <v>0.02452003655415507</v>
       </c>
       <c r="D9">
-        <v>0.9338380511602573</v>
+        <v>0.6668640573597397</v>
       </c>
       <c r="E9">
-        <v>0.3523786151006049</v>
+        <v>0.5062183628899903</v>
       </c>
       <c r="H9">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -9225,17 +9555,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9246,19 +9576,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.01106107027440365</v>
+        <v>-0.01291513840563854</v>
       </c>
       <c r="C10">
-        <v>0.03907994419590279</v>
+        <v>0.04066573712753201</v>
       </c>
       <c r="D10">
-        <v>-0.2830370027898685</v>
+        <v>-0.3175926300102545</v>
       </c>
       <c r="E10">
-        <v>0.777666318885762</v>
+        <v>0.7513800747264896</v>
       </c>
       <c r="H10">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -9267,17 +9597,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9288,19 +9618,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.04592690843300916</v>
+        <v>-0.07076033289578518</v>
       </c>
       <c r="C11">
-        <v>0.0402260370048026</v>
+        <v>0.04076620654414274</v>
       </c>
       <c r="D11">
-        <v>-1.141720931334248</v>
+        <v>-1.735759563970319</v>
       </c>
       <c r="E11">
-        <v>0.2559836577021267</v>
+        <v>0.08533223915568128</v>
       </c>
       <c r="H11">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -9309,17 +9639,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9330,19 +9660,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.2926480746710299</v>
+        <v>-0.2760657642339563</v>
       </c>
       <c r="C12">
-        <v>0.04259198236183771</v>
+        <v>0.04448412503037009</v>
       </c>
       <c r="D12">
-        <v>-6.870966281514092</v>
+        <v>-6.205938951153506</v>
       </c>
       <c r="E12">
-        <v>3.673584099632492E-10</v>
+        <v>9.221498533007008E-09</v>
       </c>
       <c r="H12">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -9351,17 +9681,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9372,19 +9702,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.02532335095332554</v>
+        <v>-0.02515959293952617</v>
       </c>
       <c r="C13">
-        <v>0.03049224543338152</v>
+        <v>0.03034306266049492</v>
       </c>
       <c r="D13">
-        <v>-0.8304849509574882</v>
+        <v>-0.8291711756665435</v>
       </c>
       <c r="E13">
-        <v>0.4080158700978338</v>
+        <v>0.4087556526248589</v>
       </c>
       <c r="H13">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9393,17 +9723,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9414,19 +9744,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.004159223393323194</v>
+        <v>-0.001615947349548189</v>
       </c>
       <c r="C14">
-        <v>0.01955431087310162</v>
+        <v>0.01948004111222685</v>
       </c>
       <c r="D14">
-        <v>-0.2127010979990356</v>
+        <v>-0.08295400098174965</v>
       </c>
       <c r="E14">
-        <v>0.8319433426259725</v>
+        <v>0.9340348845448807</v>
       </c>
       <c r="H14">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -9435,17 +9765,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9456,19 +9786,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.04881703376331528</v>
+        <v>-0.03978373624862467</v>
       </c>
       <c r="C15">
-        <v>0.04029961361284796</v>
+        <v>0.03847704743531173</v>
       </c>
       <c r="D15">
-        <v>-1.21135240234045</v>
+        <v>-1.033960215255855</v>
       </c>
       <c r="E15">
-        <v>0.2282875450839939</v>
+        <v>0.3033625197152673</v>
       </c>
       <c r="H15">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9477,17 +9807,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9498,19 +9828,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.05497995782035156</v>
+        <v>0.05786388419644095</v>
       </c>
       <c r="C16">
-        <v>0.0403789043493472</v>
+        <v>0.04076039842116546</v>
       </c>
       <c r="D16">
-        <v>1.361601031684269</v>
+        <v>1.419610367851415</v>
       </c>
       <c r="E16">
-        <v>0.1760324492111856</v>
+        <v>0.1584739806043793</v>
       </c>
       <c r="H16">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9519,17 +9849,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9540,19 +9870,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.00354125968928055</v>
+        <v>-0.004082339405974277</v>
       </c>
       <c r="C17">
-        <v>0.02527229675407199</v>
+        <v>0.02548134137590333</v>
       </c>
       <c r="D17">
-        <v>-0.140124173269292</v>
+        <v>-0.1602089680347354</v>
       </c>
       <c r="E17">
-        <v>0.8888113428158877</v>
+        <v>0.8730025051163562</v>
       </c>
       <c r="H17">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9561,17 +9891,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9582,19 +9912,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.08660815886289586</v>
+        <v>0.07044829965121222</v>
       </c>
       <c r="C18">
-        <v>0.02429216537373911</v>
+        <v>0.02501319602714585</v>
       </c>
       <c r="D18">
-        <v>3.565271252291203</v>
+        <v>2.816445350476501</v>
       </c>
       <c r="E18">
-        <v>0.0005340112644761881</v>
+        <v>0.005732032131129037</v>
       </c>
       <c r="H18">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9603,17 +9933,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9624,19 +9954,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.06264378193378928</v>
+        <v>0.07842421031269839</v>
       </c>
       <c r="C19">
-        <v>0.04946465217063051</v>
+        <v>0.04741890335271588</v>
       </c>
       <c r="D19">
-        <v>1.26643530652347</v>
+        <v>1.653859637565969</v>
       </c>
       <c r="E19">
-        <v>0.2079616447417866</v>
+        <v>0.1009314316752211</v>
       </c>
       <c r="H19">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9645,40 +9975,40 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B20">
-        <v>-2.056114780804978</v>
+        <v>-0.788384644898162</v>
       </c>
       <c r="C20">
-        <v>0.8637485757364272</v>
+        <v>0.2709114612345887</v>
       </c>
       <c r="D20">
-        <v>-2.380455190970296</v>
+        <v>-2.910119200219</v>
       </c>
       <c r="E20">
-        <v>0.01896484027342214</v>
+        <v>0.004352375396588384</v>
       </c>
       <c r="H20">
-        <v>0.539482266101875</v>
+        <v>0.5444925485150709</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9687,17 +10017,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_v | treatment_group +      period_narrow</t>
+          <t>prratio_ln ~ 1 + region_agg + info_binary + agent_type + matched_design +      audit_type + callback_type + airbnb + can_education + can_employment +      peer_reviewed + language + can_gender + prratio_ln_se | treatment_group +      period_narrow</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -9708,7 +10038,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9719,22 +10049,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -9744,8 +10109,10 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
-        <v>0.004352375396588402</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9754,13 +10121,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.07459918268758346</v>
+      </c>
+      <c r="F2">
+        <v>0.07164427365269281</v>
+      </c>
+      <c r="G2">
+        <v>-1.041244176041411</v>
+      </c>
+      <c r="H2">
+        <v>0.2977622378874329</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>0.004352375396588384</v>
       </c>
     </row>
   </sheetData>
@@ -10178,19 +10563,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.004121171687688115</v>
+        <v>-0.001647878058056503</v>
       </c>
       <c r="C2">
-        <v>0.03955533202768703</v>
+        <v>0.03895152897653532</v>
       </c>
       <c r="D2">
-        <v>0.104187513450866</v>
+        <v>-0.04230586324478292</v>
       </c>
       <c r="E2">
-        <v>0.9172052397295867</v>
+        <v>0.9663295339607658</v>
       </c>
       <c r="H2">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -10199,17 +10584,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10220,19 +10605,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.0845524860540956</v>
+        <v>0.09235934072423779</v>
       </c>
       <c r="C3">
-        <v>0.1197096873432897</v>
+        <v>0.1155583127924401</v>
       </c>
       <c r="D3">
-        <v>0.70631281336176</v>
+        <v>0.7992444549630011</v>
       </c>
       <c r="E3">
-        <v>0.4814474036493279</v>
+        <v>0.4258254813028494</v>
       </c>
       <c r="H3">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -10241,17 +10626,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10262,19 +10647,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.009526996880488962</v>
+        <v>0.003471659254375953</v>
       </c>
       <c r="C4">
-        <v>0.06718977190393235</v>
+        <v>0.07602182593424615</v>
       </c>
       <c r="D4">
-        <v>0.14179236825079</v>
+        <v>0.04566661234075998</v>
       </c>
       <c r="E4">
-        <v>0.8874965005457166</v>
+        <v>0.963656581210941</v>
       </c>
       <c r="H4">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -10283,17 +10668,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10304,19 +10689,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1784447132447703</v>
+        <v>0.1631265450136439</v>
       </c>
       <c r="C5">
-        <v>0.06526143669513805</v>
+        <v>0.07163831562401195</v>
       </c>
       <c r="D5">
-        <v>2.734305621838454</v>
+        <v>2.277085154678967</v>
       </c>
       <c r="E5">
-        <v>0.00725914657380757</v>
+        <v>0.02466328207330423</v>
       </c>
       <c r="H5">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -10325,17 +10710,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10346,19 +10731,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.122439353406885</v>
+        <v>0.1220010467675942</v>
       </c>
       <c r="C6">
-        <v>0.05541266752376676</v>
+        <v>0.06465499370788161</v>
       </c>
       <c r="D6">
-        <v>2.209591396306091</v>
+        <v>1.88695473885294</v>
       </c>
       <c r="E6">
-        <v>0.02914993702195446</v>
+        <v>0.06173254737887613</v>
       </c>
       <c r="H6">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -10367,17 +10752,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10388,19 +10773,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.0925226365264708</v>
+        <v>0.1014986659526316</v>
       </c>
       <c r="C7">
-        <v>0.06352377763449386</v>
+        <v>0.07166584602406162</v>
       </c>
       <c r="D7">
-        <v>1.456504004828427</v>
+        <v>1.416276672692229</v>
       </c>
       <c r="E7">
-        <v>0.14802638262707</v>
+        <v>0.1594452190357281</v>
       </c>
       <c r="H7">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -10409,17 +10794,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10430,19 +10815,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.002478241051090964</v>
+        <v>0.0005019615800688423</v>
       </c>
       <c r="C8">
-        <v>0.02769345534683254</v>
+        <v>0.02757614882318517</v>
       </c>
       <c r="D8">
-        <v>-0.08948832928406726</v>
+        <v>0.01820274409190918</v>
       </c>
       <c r="E8">
-        <v>0.9288522462627267</v>
+        <v>0.9855092149570779</v>
       </c>
       <c r="H8">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -10451,17 +10836,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10472,19 +10857,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.1498837365168991</v>
+        <v>0.1385496200635432</v>
       </c>
       <c r="C9">
-        <v>0.03517064923276978</v>
+        <v>0.03605354007276145</v>
       </c>
       <c r="D9">
-        <v>4.261614152326962</v>
+        <v>3.842885325100649</v>
       </c>
       <c r="E9">
-        <v>4.223646174662828E-05</v>
+        <v>0.0002013177549710959</v>
       </c>
       <c r="H9">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -10493,17 +10878,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10514,19 +10899,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.08971717281881678</v>
+        <v>0.07634729074696087</v>
       </c>
       <c r="C10">
-        <v>0.0379767825741117</v>
+        <v>0.0397228749437344</v>
       </c>
       <c r="D10">
-        <v>2.362421636001778</v>
+        <v>1.921998114565052</v>
       </c>
       <c r="E10">
-        <v>0.01986595388409408</v>
+        <v>0.05712406769734917</v>
       </c>
       <c r="H10">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -10535,17 +10920,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10556,19 +10941,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.05413407657369779</v>
+        <v>-0.06263734528633395</v>
       </c>
       <c r="C11">
-        <v>0.02236044758958806</v>
+        <v>0.02222856744790471</v>
       </c>
       <c r="D11">
-        <v>-2.420974640905883</v>
+        <v>-2.817875935241082</v>
       </c>
       <c r="E11">
-        <v>0.01707105861326417</v>
+        <v>0.005708251987153271</v>
       </c>
       <c r="H11">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -10577,17 +10962,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10598,19 +10983,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.06393148506595499</v>
+        <v>-0.06552123448932023</v>
       </c>
       <c r="C12">
-        <v>0.03095033938887191</v>
+        <v>0.03174346849999931</v>
       </c>
       <c r="D12">
-        <v>-2.065614992543227</v>
+        <v>-2.064085545324754</v>
       </c>
       <c r="E12">
-        <v>0.04115188134419719</v>
+        <v>0.04129934331832508</v>
       </c>
       <c r="H12">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -10619,17 +11004,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10640,19 +11025,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.02065930720435492</v>
+        <v>-0.02669251916505307</v>
       </c>
       <c r="C13">
-        <v>0.02180066598682125</v>
+        <v>0.02206841252077932</v>
       </c>
       <c r="D13">
-        <v>-0.9476456919638926</v>
+        <v>-1.209535082775879</v>
       </c>
       <c r="E13">
-        <v>0.3453320299678814</v>
+        <v>0.228981769037455</v>
       </c>
       <c r="H13">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -10661,17 +11046,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10682,19 +11067,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.05370609311737354</v>
+        <v>0.05006750072431261</v>
       </c>
       <c r="C14">
-        <v>0.04740853023386768</v>
+        <v>0.04705339901303471</v>
       </c>
       <c r="D14">
-        <v>1.132836070902004</v>
+        <v>1.064057045282593</v>
       </c>
       <c r="E14">
-        <v>0.2596810487143756</v>
+        <v>0.2895713671130761</v>
       </c>
       <c r="H14">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -10703,17 +11088,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10724,19 +11109,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.06414548613949569</v>
+        <v>-0.08782854339792892</v>
       </c>
       <c r="C15">
-        <v>0.0458557596090628</v>
+        <v>0.04574814691175681</v>
       </c>
       <c r="D15">
-        <v>-1.398853419643672</v>
+        <v>-1.919827344424259</v>
       </c>
       <c r="E15">
-        <v>0.1645956910782456</v>
+        <v>0.05740086835422962</v>
       </c>
       <c r="H15">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -10745,17 +11130,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10766,19 +11151,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.2861736707601849</v>
+        <v>-0.2700127917454321</v>
       </c>
       <c r="C16">
-        <v>0.04690613195762495</v>
+        <v>0.0426222203188423</v>
       </c>
       <c r="D16">
-        <v>-6.100986349049512</v>
+        <v>-6.335024072550856</v>
       </c>
       <c r="E16">
-        <v>1.513858510309782E-08</v>
+        <v>4.986392430445097E-09</v>
       </c>
       <c r="H16">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -10787,17 +11172,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10808,19 +11193,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.01671265574087295</v>
+        <v>-0.01663313152629937</v>
       </c>
       <c r="C17">
-        <v>0.02924527291412132</v>
+        <v>0.02889347622120489</v>
       </c>
       <c r="D17">
-        <v>-0.5714652002034527</v>
+        <v>-0.5756708330613518</v>
       </c>
       <c r="E17">
-        <v>0.5688192674951982</v>
+        <v>0.5659823562448227</v>
       </c>
       <c r="H17">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -10829,17 +11214,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10850,19 +11235,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.007693059876997542</v>
+        <v>-0.00513673151219444</v>
       </c>
       <c r="C18">
-        <v>0.01603116277166205</v>
+        <v>0.01559149817841269</v>
       </c>
       <c r="D18">
-        <v>-0.479881589786887</v>
+        <v>-0.3294572114504387</v>
       </c>
       <c r="E18">
-        <v>0.6322391638429015</v>
+        <v>0.7424200253502088</v>
       </c>
       <c r="H18">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -10871,17 +11256,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10892,19 +11277,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.03271961242739749</v>
+        <v>-0.02389523194587107</v>
       </c>
       <c r="C19">
-        <v>0.03373716125957189</v>
+        <v>0.03149173985101553</v>
       </c>
       <c r="D19">
-        <v>-0.9698389314872868</v>
+        <v>-0.7587777639126061</v>
       </c>
       <c r="E19">
-        <v>0.3341980942650455</v>
+        <v>0.4495653087244116</v>
       </c>
       <c r="H19">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -10913,17 +11298,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10934,19 +11319,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.02041418506245529</v>
+        <v>0.02482441804552615</v>
       </c>
       <c r="C20">
-        <v>0.03221886549632606</v>
+        <v>0.03267413687169182</v>
       </c>
       <c r="D20">
-        <v>0.6336096801665204</v>
+        <v>0.7597574235245826</v>
       </c>
       <c r="E20">
-        <v>0.5276159804885412</v>
+        <v>0.4489817493323047</v>
       </c>
       <c r="H20">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -10955,17 +11340,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -10976,19 +11361,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.0228331564216185</v>
+        <v>0.02240212419099332</v>
       </c>
       <c r="C21">
-        <v>0.01950026703390818</v>
+        <v>0.01969789974971522</v>
       </c>
       <c r="D21">
-        <v>1.170915063979119</v>
+        <v>1.137284912383474</v>
       </c>
       <c r="E21">
-        <v>0.2440962010223643</v>
+        <v>0.257825027146338</v>
       </c>
       <c r="H21">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -10997,17 +11382,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11018,19 +11403,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.1029680356990681</v>
+        <v>0.08605214730046495</v>
       </c>
       <c r="C22">
-        <v>0.02648800237337721</v>
+        <v>0.02705710876139709</v>
       </c>
       <c r="D22">
-        <v>3.887346212357641</v>
+        <v>3.18038959961743</v>
       </c>
       <c r="E22">
-        <v>0.0001714201124437524</v>
+        <v>0.001898641698189092</v>
       </c>
       <c r="H22">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11039,17 +11424,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11060,19 +11445,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.03410388396788339</v>
+        <v>0.05312302157698209</v>
       </c>
       <c r="C23">
-        <v>0.04541963878843042</v>
+        <v>0.04429549958145537</v>
       </c>
       <c r="D23">
-        <v>0.7508620693075735</v>
+        <v>1.199287107695754</v>
       </c>
       <c r="E23">
-        <v>0.4542964533511149</v>
+        <v>0.2329250520978671</v>
       </c>
       <c r="H23">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -11081,40 +11466,40 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B24">
-        <v>-2.321949513257747</v>
+        <v>-0.8407065876651971</v>
       </c>
       <c r="C24">
-        <v>0.8992238441448547</v>
+        <v>0.2673893511089995</v>
       </c>
       <c r="D24">
-        <v>-2.582170755787597</v>
+        <v>-3.144128904828707</v>
       </c>
       <c r="E24">
-        <v>0.01109623250102514</v>
+        <v>0.002128523510632167</v>
       </c>
       <c r="H24">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -11123,17 +11508,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11144,19 +11529,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.2629855181450281</v>
+        <v>0.2632735827828565</v>
       </c>
       <c r="C25">
-        <v>0.05901356210229469</v>
+        <v>0.06070857003370786</v>
       </c>
       <c r="D25">
-        <v>4.456357297821922</v>
+        <v>4.336679032905508</v>
       </c>
       <c r="E25">
-        <v>1.972989154441122E-05</v>
+        <v>3.157699032610712E-05</v>
       </c>
       <c r="H25">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -11165,17 +11550,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11186,19 +11571,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.03012099534401944</v>
+        <v>0.03522747572235828</v>
       </c>
       <c r="C26">
-        <v>0.05292414464983979</v>
+        <v>0.05239594728761118</v>
       </c>
       <c r="D26">
-        <v>0.56913523200626</v>
+        <v>0.6723320704364415</v>
       </c>
       <c r="E26">
-        <v>0.5703939066073924</v>
+        <v>0.5027447551795576</v>
       </c>
       <c r="H26">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11207,17 +11592,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11228,19 +11613,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.501483317749033</v>
+        <v>-0.5036953976850678</v>
       </c>
       <c r="C27">
-        <v>0.1429929427403039</v>
+        <v>0.1375977262005145</v>
       </c>
       <c r="D27">
-        <v>-3.507049425927265</v>
+        <v>-3.660637509017095</v>
       </c>
       <c r="E27">
-        <v>0.0006511116122632854</v>
+        <v>0.0003840895289768303</v>
       </c>
       <c r="H27">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11249,17 +11634,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11270,19 +11655,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.2054646811506475</v>
+        <v>-0.221538029045578</v>
       </c>
       <c r="C28">
-        <v>0.136747111377021</v>
+        <v>0.1332758182639725</v>
       </c>
       <c r="D28">
-        <v>-1.502515695444327</v>
+        <v>-1.662252251993599</v>
       </c>
       <c r="E28">
-        <v>0.1357534658906441</v>
+        <v>0.09923383347934961</v>
       </c>
       <c r="H28">
-        <v>0.5877932458325286</v>
+        <v>0.5924249236632224</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -11291,17 +11676,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v + region_agg:period_narrow | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + period_narrow + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se + region_agg:period_narrow | treatment_group</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11697,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11323,22 +11708,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>pet_p_value</t>
+          <t>pet_status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pet_status</t>
+          <t>peese_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>peese_status</t>
+          <t>selected_model</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>selected_model</t>
+          <t>bc_estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>bc_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bc_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bc_p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bc_alpha</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bc_direction_used</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>selector_note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pet_term_p_value_diag</t>
         </is>
       </c>
     </row>
@@ -11348,23 +11768,43 @@
           <t>overall</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.07291754386542018</v>
+      </c>
+      <c r="F2">
+        <v>0.09895501140176161</v>
+      </c>
+      <c r="G2">
+        <v>-0.7368757057626097</v>
+      </c>
+      <c r="H2">
+        <v>0.4611979391832178</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="L2">
         <v>0.002128523510632167</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>peese</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -11662,7 +12102,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.163*** (0.037)</t>
+          <t>0.139*** (0.038)</t>
         </is>
       </c>
     </row>
@@ -11674,7 +12114,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.097** (0.037)</t>
+          <t>0.075 (0.039)</t>
         </is>
       </c>
     </row>
@@ -11686,7 +12126,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.020 (0.039)</t>
+          <t>0.048 (0.039)</t>
         </is>
       </c>
     </row>
@@ -11698,7 +12138,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.019 (0.041)</t>
+          <t>-0.024 (0.045)</t>
         </is>
       </c>
     </row>
@@ -11710,7 +12150,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.297*** (0.055)</t>
+          <t>-0.243*** (0.052)</t>
         </is>
       </c>
     </row>
@@ -11722,7 +12162,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.086** (0.029)</t>
+          <t>-0.080** (0.029)</t>
         </is>
       </c>
     </row>
@@ -11734,7 +12174,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.036* (0.018)</t>
+          <t>0.031 (0.018)</t>
         </is>
       </c>
     </row>
@@ -11746,7 +12186,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.046 (0.027)</t>
+          <t>0.013 (0.028)</t>
         </is>
       </c>
     </row>
@@ -11758,19 +12198,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.096 (0.069)</t>
+          <t>0.139* (0.065)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-2.857* (1.216)</t>
+          <t>-1.303*** (0.330)</t>
         </is>
       </c>
     </row>
@@ -11806,7 +12246,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.672</t>
         </is>
       </c>
     </row>
@@ -11818,7 +12258,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -11957,7 +12397,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-2.898 (6.348)</t>
+          <t>-0.217** (0.064)</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12791,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.017 (13.267)</t>
+          <t>0.081* (0.034)</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12803,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-72.291** (25.101)</t>
+          <t>-0.285*** (0.070)</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12815,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.005 (0.004)</t>
+          <t>0.008 (0.004)</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12827,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.136** (0.043)</t>
+          <t>0.122** (0.043)</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12839,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.050 (0.042)</t>
+          <t>0.038 (0.042)</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12851,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.064* (0.030)</t>
+          <t>-0.069* (0.029)</t>
         </is>
       </c>
     </row>
@@ -12423,7 +12863,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.074 (0.042)</t>
+          <t>-0.108* (0.043)</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12875,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.258*** (0.042)</t>
+          <t>-0.235*** (0.039)</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12887,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.002 (0.031)</t>
+          <t>-0.003 (0.030)</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12899,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.000 (0.024)</t>
+          <t>0.003 (0.023)</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12911,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.070* (0.029)</t>
+          <t>0.048 (0.029)</t>
         </is>
       </c>
     </row>
@@ -12483,19 +12923,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.091* (0.044)</t>
+          <t>0.103* (0.040)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-2.905** (1.077)</t>
+          <t>-1.162*** (0.285)</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12947,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.011 (0.007)</t>
+          <t>-0.013* (0.007)</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12995,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>0.557</t>
         </is>
       </c>
     </row>
@@ -12567,7 +13007,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -12625,7 +13065,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.107** (0.035)</t>
+          <t>0.103** (0.034)</t>
         </is>
       </c>
     </row>
@@ -12637,7 +13077,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.074 (0.065)</t>
+          <t>-0.077 (0.064)</t>
         </is>
       </c>
     </row>
@@ -12649,7 +13089,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.154*** (0.046)</t>
+          <t>0.145** (0.047)</t>
         </is>
       </c>
     </row>
@@ -12661,7 +13101,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.080 (0.051)</t>
+          <t>0.068 (0.053)</t>
         </is>
       </c>
     </row>
@@ -12673,7 +13113,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.115** (0.034)</t>
+          <t>-0.117** (0.035)</t>
         </is>
       </c>
     </row>
@@ -12685,7 +13125,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.046 (0.040)</t>
+          <t>-0.071 (0.041)</t>
         </is>
       </c>
     </row>
@@ -12697,7 +13137,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.293*** (0.043)</t>
+          <t>-0.276*** (0.044)</t>
         </is>
       </c>
     </row>
@@ -12733,7 +13173,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.087*** (0.024)</t>
+          <t>0.070** (0.025)</t>
         </is>
       </c>
     </row>
@@ -12745,19 +13185,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.063 (0.049)</t>
+          <t>0.078 (0.047)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-2.056* (0.864)</t>
+          <t>-0.788** (0.271)</t>
         </is>
       </c>
     </row>
@@ -12793,7 +13233,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.544</t>
         </is>
       </c>
     </row>
@@ -12805,7 +13245,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -12863,7 +13303,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.004 (0.040)</t>
+          <t>-0.002 (0.039)</t>
         </is>
       </c>
     </row>
@@ -12875,7 +13315,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.085 (0.120)</t>
+          <t>0.092 (0.116)</t>
         </is>
       </c>
     </row>
@@ -12887,7 +13327,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.010 (0.067)</t>
+          <t>0.003 (0.076)</t>
         </is>
       </c>
     </row>
@@ -12899,7 +13339,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.178** (0.065)</t>
+          <t>0.163* (0.072)</t>
         </is>
       </c>
     </row>
@@ -12911,7 +13351,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.122* (0.055)</t>
+          <t>0.122 (0.065)</t>
         </is>
       </c>
     </row>
@@ -12923,7 +13363,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.093 (0.064)</t>
+          <t>0.101 (0.072)</t>
         </is>
       </c>
     </row>
@@ -12935,7 +13375,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.150*** (0.035)</t>
+          <t>0.139*** (0.036)</t>
         </is>
       </c>
     </row>
@@ -12947,7 +13387,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.090* (0.038)</t>
+          <t>0.076 (0.040)</t>
         </is>
       </c>
     </row>
@@ -12959,7 +13399,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.064* (0.031)</t>
+          <t>-0.066* (0.032)</t>
         </is>
       </c>
     </row>
@@ -12971,7 +13411,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.064 (0.046)</t>
+          <t>-0.088 (0.046)</t>
         </is>
       </c>
     </row>
@@ -12983,7 +13423,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.286*** (0.047)</t>
+          <t>-0.270*** (0.043)</t>
         </is>
       </c>
     </row>
@@ -13007,7 +13447,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.023 (0.020)</t>
+          <t>0.022 (0.020)</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13459,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.103*** (0.026)</t>
+          <t>0.086** (0.027)</t>
         </is>
       </c>
     </row>
@@ -13031,19 +13471,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.034 (0.045)</t>
+          <t>0.053 (0.044)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-2.322* (0.899)</t>
+          <t>-0.841** (0.267)</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13495,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.263*** (0.059)</t>
+          <t>0.263*** (0.061)</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13507,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.030 (0.053)</t>
+          <t>0.035 (0.052)</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13519,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-0.501*** (0.143)</t>
+          <t>-0.504*** (0.138)</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13531,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-0.205 (0.137)</t>
+          <t>-0.222 (0.133)</t>
         </is>
       </c>
     </row>
@@ -13127,7 +13567,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>0.592</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13579,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13256,19 +13696,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.106413270326769</v>
+        <v>0.09982605016882504</v>
       </c>
       <c r="C2">
-        <v>0.03451570138406117</v>
+        <v>0.03467122349159463</v>
       </c>
       <c r="D2">
-        <v>3.083039488106971</v>
+        <v>2.879219136671827</v>
       </c>
       <c r="E2">
-        <v>0.002575121825083347</v>
+        <v>0.004769550717660471</v>
       </c>
       <c r="H2">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -13277,17 +13717,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13298,19 +13738,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.09740027293870693</v>
+        <v>-0.1002039733581521</v>
       </c>
       <c r="C3">
-        <v>0.06122436333275564</v>
+        <v>0.0592430811613901</v>
       </c>
       <c r="D3">
-        <v>-1.590874410720035</v>
+        <v>-1.691403812795899</v>
       </c>
       <c r="E3">
-        <v>0.1144316612170198</v>
+        <v>0.09351589115856521</v>
       </c>
       <c r="H3">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -13319,17 +13759,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13340,19 +13780,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0009283625785040308</v>
+        <v>0.00192655725587774</v>
       </c>
       <c r="C4">
-        <v>0.003273556331067501</v>
+        <v>0.003330125209974789</v>
       </c>
       <c r="D4">
-        <v>0.2835945023134193</v>
+        <v>0.5785239696414675</v>
       </c>
       <c r="E4">
-        <v>0.7772400871316719</v>
+        <v>0.5640616984236699</v>
       </c>
       <c r="H4">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -13361,17 +13801,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13382,19 +13822,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.06170622415069042</v>
+        <v>-0.06011806511300141</v>
       </c>
       <c r="C5">
-        <v>0.02858754964695033</v>
+        <v>0.02854689961970789</v>
       </c>
       <c r="D5">
-        <v>-2.158499938355967</v>
+        <v>-2.105940256695959</v>
       </c>
       <c r="E5">
-        <v>0.03300454083358163</v>
+        <v>0.03742378664450501</v>
       </c>
       <c r="H5">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -13403,17 +13843,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13424,19 +13864,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1461186329665994</v>
+        <v>0.1366845305351378</v>
       </c>
       <c r="C6">
-        <v>0.04477799420806662</v>
+        <v>0.04584657091174827</v>
       </c>
       <c r="D6">
-        <v>3.263179504817492</v>
+        <v>2.981346866666361</v>
       </c>
       <c r="E6">
-        <v>0.001457579115684712</v>
+        <v>0.003515288552941591</v>
       </c>
       <c r="H6">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -13445,17 +13885,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13466,19 +13906,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.05288324797046944</v>
+        <v>0.0435943077681387</v>
       </c>
       <c r="C7">
-        <v>0.04356245713342186</v>
+        <v>0.04369970863186159</v>
       </c>
       <c r="D7">
-        <v>1.213963845255563</v>
+        <v>0.9975880648401843</v>
       </c>
       <c r="E7">
-        <v>0.2272926243488815</v>
+        <v>0.3206105883648853</v>
       </c>
       <c r="H7">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -13487,17 +13927,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13508,19 +13948,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.04384073062687397</v>
+        <v>-0.05381728404476497</v>
       </c>
       <c r="C8">
-        <v>0.02771174396442786</v>
+        <v>0.02647691241942692</v>
       </c>
       <c r="D8">
-        <v>-1.58202712478688</v>
+        <v>-2.032611778602915</v>
       </c>
       <c r="E8">
-        <v>0.1164383665609353</v>
+        <v>0.04443610697259316</v>
       </c>
       <c r="H8">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -13529,17 +13969,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13550,19 +13990,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.09188515326712232</v>
+        <v>-0.09807994590470519</v>
       </c>
       <c r="C9">
-        <v>0.03211288313671219</v>
+        <v>0.03251507328091832</v>
       </c>
       <c r="D9">
-        <v>-2.861317461778357</v>
+        <v>-3.016445482294638</v>
       </c>
       <c r="E9">
-        <v>0.005027706786902356</v>
+        <v>0.003159877366344831</v>
       </c>
       <c r="H9">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -13571,17 +14011,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13592,19 +14032,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.01186326311506588</v>
+        <v>0.007482226903929013</v>
       </c>
       <c r="C10">
-        <v>0.02383951061765404</v>
+        <v>0.02441729600510544</v>
       </c>
       <c r="D10">
-        <v>0.4976303123555184</v>
+        <v>0.3064314288676578</v>
       </c>
       <c r="E10">
-        <v>0.6197116310202598</v>
+        <v>0.7598400799118095</v>
       </c>
       <c r="H10">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -13613,17 +14053,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13634,19 +14074,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.005323866991633027</v>
+        <v>-0.002755144749566445</v>
       </c>
       <c r="C11">
-        <v>0.04525325890601063</v>
+        <v>0.04535142657093318</v>
       </c>
       <c r="D11">
-        <v>0.1176460462812304</v>
+        <v>-0.0607510051587282</v>
       </c>
       <c r="E11">
-        <v>0.9065569773528463</v>
+        <v>0.9516648268955632</v>
       </c>
       <c r="H11">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -13655,17 +14095,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13676,19 +14116,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.06292188611160597</v>
+        <v>-0.09166024725529612</v>
       </c>
       <c r="C12">
-        <v>0.04329661503715649</v>
+        <v>0.04457675040357974</v>
       </c>
       <c r="D12">
-        <v>-1.453274951346829</v>
+        <v>-2.056234391817294</v>
       </c>
       <c r="E12">
-        <v>0.1489189486603042</v>
+        <v>0.0420634729305578</v>
       </c>
       <c r="H12">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -13697,17 +14137,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13718,19 +14158,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.283055917747331</v>
+        <v>-0.2668345190370716</v>
       </c>
       <c r="C13">
-        <v>0.04153190532087628</v>
+        <v>0.0441333402742396</v>
       </c>
       <c r="D13">
-        <v>-6.815384836318865</v>
+        <v>-6.046098423074073</v>
       </c>
       <c r="E13">
-        <v>4.833211888397194E-10</v>
+        <v>1.958870083743496E-08</v>
       </c>
       <c r="H13">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -13739,17 +14179,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13760,19 +14200,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.01671730067752867</v>
+        <v>-0.02130928550846506</v>
       </c>
       <c r="C14">
-        <v>0.03177325620999805</v>
+        <v>0.03140385186640629</v>
       </c>
       <c r="D14">
-        <v>-0.5261437659092761</v>
+        <v>-0.6785564267439527</v>
       </c>
       <c r="E14">
-        <v>0.5998194489996362</v>
+        <v>0.4988062643529936</v>
       </c>
       <c r="H14">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -13781,17 +14221,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13802,19 +14242,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.001860796553951371</v>
+        <v>0.001989798426744267</v>
       </c>
       <c r="C15">
-        <v>0.01981454487113199</v>
+        <v>0.01994233817279491</v>
       </c>
       <c r="D15">
-        <v>-0.09391063817278909</v>
+        <v>0.09977758924270602</v>
       </c>
       <c r="E15">
-        <v>0.925346456016101</v>
+        <v>0.9206977019072403</v>
       </c>
       <c r="H15">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -13823,17 +14263,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13844,19 +14284,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.06851099767159019</v>
+        <v>-0.05425491772165255</v>
       </c>
       <c r="C16">
-        <v>0.03538282934095147</v>
+        <v>0.03428141870918724</v>
       </c>
       <c r="D16">
-        <v>-1.936278102901645</v>
+        <v>-1.582633384630389</v>
       </c>
       <c r="E16">
-        <v>0.0553310960724333</v>
+        <v>0.1162999689979592</v>
       </c>
       <c r="H16">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -13865,17 +14305,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13886,19 +14326,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.06459610952573473</v>
+        <v>0.06579813109438143</v>
       </c>
       <c r="C17">
-        <v>0.03628902626198894</v>
+        <v>0.03668059452307389</v>
       </c>
       <c r="D17">
-        <v>1.780045269315924</v>
+        <v>1.793813103356086</v>
       </c>
       <c r="E17">
-        <v>0.07775631711288565</v>
+        <v>0.07551738559015589</v>
       </c>
       <c r="H17">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -13907,17 +14347,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13928,19 +14368,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.004657008994339734</v>
+        <v>-0.00365936074605032</v>
       </c>
       <c r="C18">
-        <v>0.0268251510452965</v>
+        <v>0.0270172373309468</v>
       </c>
       <c r="D18">
-        <v>-0.1736060679202137</v>
+        <v>-0.1354454084710844</v>
       </c>
       <c r="E18">
-        <v>0.8624856773055023</v>
+        <v>0.8925007065190245</v>
       </c>
       <c r="H18">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -13949,17 +14389,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -13970,19 +14410,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.07808156699598899</v>
+        <v>0.05902691274330336</v>
       </c>
       <c r="C19">
-        <v>0.02655694494402426</v>
+        <v>0.02687179769641682</v>
       </c>
       <c r="D19">
-        <v>2.940156225069051</v>
+        <v>2.196611979970891</v>
       </c>
       <c r="E19">
-        <v>0.003979232985962768</v>
+        <v>0.03009001139016601</v>
       </c>
       <c r="H19">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -13991,17 +14431,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
@@ -14012,19 +14452,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.09586646997263584</v>
+        <v>0.1054557549033393</v>
       </c>
       <c r="C20">
-        <v>0.04287927238710344</v>
+        <v>0.03878399114919229</v>
       </c>
       <c r="D20">
-        <v>2.235729867502814</v>
+        <v>2.719053706919368</v>
       </c>
       <c r="E20">
-        <v>0.02733422676403852</v>
+        <v>0.007580467780421207</v>
       </c>
       <c r="H20">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -14033,40 +14473,40 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>prratio_ln_v</t>
+          <t>prratio_ln_se</t>
         </is>
       </c>
       <c r="B21">
-        <v>-2.487064164583419</v>
+        <v>-0.9763533694926849</v>
       </c>
       <c r="C21">
-        <v>0.9516659402170078</v>
+        <v>0.2636278112990947</v>
       </c>
       <c r="D21">
-        <v>-2.613379400776175</v>
+        <v>-3.703529474684212</v>
       </c>
       <c r="E21">
-        <v>0.01018540313876409</v>
+        <v>0.0003305452882659248</v>
       </c>
       <c r="H21">
-        <v>0.5262026321618308</v>
+        <v>0.5355926496276522</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -14075,17 +14515,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_v | treatment_group</t>
+          <t>prratio_ln ~ 1 + region_agg + year_mid + info_binary + agent_type +      matched_design + audit_type + callback_type + airbnb + can_education +      can_employment + peer_reviewed + language + can_gender +      prratio_ln_se | treatment_group</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>peese</t>
+          <t>pet</t>
         </is>
       </c>
     </row>
